--- a/football_stats.xlsx
+++ b/football_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\football_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231626FD-D60D-4CEF-9C20-6BB9EC8E0560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01754BC2-ED51-4782-A5B4-816504F354F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14340" yWindow="0" windowWidth="14205" windowHeight="14775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2212" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2276" uniqueCount="137">
   <si>
     <t>player_id</t>
   </si>
@@ -458,6 +458,15 @@
   <si>
     <t>Гоша (Юра +1)</t>
   </si>
+  <si>
+    <t>Рус (Рыжий +1)</t>
+  </si>
+  <si>
+    <t>Ден (Зидан +1)</t>
+  </si>
+  <si>
+    <t>Арги</t>
+  </si>
 </sst>
 </file>
 
@@ -466,7 +475,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,6 +519,19 @@
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -644,7 +666,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -759,6 +781,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1308,8 +1339,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G117" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
-  <autoFilter ref="A1:G117" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G120" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
+  <autoFilter ref="A1:G120" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G74">
     <sortCondition descending="1" ref="G1:G74"/>
   </sortState>
@@ -1337,8 +1368,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J914" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A1:J914" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J941" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:J941" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G60">
     <sortCondition ref="A1:A60"/>
   </sortState>
@@ -1365,8 +1396,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E133" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E133" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E137" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E137" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{92BE0DCE-EF0C-43B2-937D-640EBFF087A6}" name="date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{B497FB59-180E-4B72-9ECD-E25C88173489}" name="team_number" dataDxfId="3"/>
@@ -1644,7 +1675,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" style="38" bestFit="1" customWidth="1"/>
@@ -1752,7 +1783,7 @@
       </c>
       <c r="E4" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F4" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1760,7 +1791,7 @@
       </c>
       <c r="G4" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1776,11 +1807,11 @@
       </c>
       <c r="D5" s="21">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="21">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F5" s="22">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1788,7 +1819,7 @@
       </c>
       <c r="G5" s="22">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1808,7 +1839,7 @@
       </c>
       <c r="E6" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F6" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1816,7 +1847,7 @@
       </c>
       <c r="G6" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1860,11 +1891,11 @@
       </c>
       <c r="D8" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F8" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1872,7 +1903,7 @@
       </c>
       <c r="G8" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1968,15 +1999,15 @@
       </c>
       <c r="C12" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F12" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1984,7 +2015,7 @@
       </c>
       <c r="G12" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2024,15 +2055,15 @@
       </c>
       <c r="C14" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D14" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F14" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2040,7 +2071,7 @@
       </c>
       <c r="G14" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2172,7 +2203,7 @@
       </c>
       <c r="E19" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2180,7 +2211,7 @@
       </c>
       <c r="G19" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2224,11 +2255,11 @@
       </c>
       <c r="D21" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F21" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2236,7 +2267,7 @@
       </c>
       <c r="G21" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2248,7 +2279,7 @@
       </c>
       <c r="C22" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2256,7 +2287,7 @@
       </c>
       <c r="E22" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F22" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2264,7 +2295,7 @@
       </c>
       <c r="G22" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2368,7 +2399,7 @@
       </c>
       <c r="E26" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F26" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2376,7 +2407,7 @@
       </c>
       <c r="G26" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2396,7 +2427,7 @@
       </c>
       <c r="E27" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F27" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2404,7 +2435,7 @@
       </c>
       <c r="G27" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2536,7 +2567,7 @@
       </c>
       <c r="E32" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F32" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2544,7 +2575,7 @@
       </c>
       <c r="G32" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2616,11 +2647,11 @@
       </c>
       <c r="D35" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E35" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F35" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2628,7 +2659,7 @@
       </c>
       <c r="G35" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2704,7 +2735,7 @@
       </c>
       <c r="E38" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F38" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2712,7 +2743,7 @@
       </c>
       <c r="G38" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2732,7 +2763,7 @@
       </c>
       <c r="E39" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F39" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2740,7 +2771,7 @@
       </c>
       <c r="G39" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2780,7 +2811,7 @@
       </c>
       <c r="C41" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D41" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2788,7 +2819,7 @@
       </c>
       <c r="E41" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F41" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2796,7 +2827,7 @@
       </c>
       <c r="G41" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2808,7 +2839,7 @@
       </c>
       <c r="C42" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D42" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2816,7 +2847,7 @@
       </c>
       <c r="E42" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F42" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2824,7 +2855,7 @@
       </c>
       <c r="G42" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2836,7 +2867,7 @@
       </c>
       <c r="C43" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D43" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2844,7 +2875,7 @@
       </c>
       <c r="E43" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F43" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2852,7 +2883,7 @@
       </c>
       <c r="G43" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3040,7 +3071,7 @@
       </c>
       <c r="E50" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F50" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3048,7 +3079,7 @@
       </c>
       <c r="G50" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3424,15 +3455,15 @@
       </c>
       <c r="C64" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D64" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E64" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F64" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3440,7 +3471,7 @@
       </c>
       <c r="G64" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3516,7 +3547,7 @@
       </c>
       <c r="E67" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F67" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3524,7 +3555,7 @@
       </c>
       <c r="G67" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3572,7 +3603,7 @@
       </c>
       <c r="E69" s="7">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F69" s="8">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3580,7 +3611,7 @@
       </c>
       <c r="G69" s="8">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3760,7 +3791,7 @@
       </c>
       <c r="C76" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D76" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3768,7 +3799,7 @@
       </c>
       <c r="E76" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F76" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3776,7 +3807,7 @@
       </c>
       <c r="G76" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -4720,7 +4751,7 @@
       </c>
       <c r="E110" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F110" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -4728,7 +4759,7 @@
       </c>
       <c r="G110" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -4925,6 +4956,90 @@
       <c r="G117" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
         <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A118" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="B118" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="C118" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>3</v>
+      </c>
+      <c r="D118" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="E118" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>6</v>
+      </c>
+      <c r="F118" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="G118" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A119" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="B119" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="C119" s="16">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D119" s="16">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E119" s="16">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="F119" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="G119" s="17">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="B120" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="C120" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>2</v>
+      </c>
+      <c r="D120" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>3</v>
+      </c>
+      <c r="E120" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>6</v>
+      </c>
+      <c r="F120" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="G120" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -4940,7 +5055,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:J914"/>
+  <dimension ref="A1:J941"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -36937,6 +37052,951 @@
       </c>
       <c r="J914" s="10" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="915" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A915" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B915" s="11">
+        <v>3</v>
+      </c>
+      <c r="C915" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D915" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Нурик</v>
+      </c>
+      <c r="E915" s="11">
+        <v>0</v>
+      </c>
+      <c r="F915" s="11">
+        <v>1</v>
+      </c>
+      <c r="G915" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H915" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I915" s="41">
+        <v>0</v>
+      </c>
+      <c r="J915" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="916" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A916" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B916" s="11">
+        <v>1</v>
+      </c>
+      <c r="C916" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D916" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Влад</v>
+      </c>
+      <c r="E916" s="11">
+        <v>0</v>
+      </c>
+      <c r="F916" s="11">
+        <v>1</v>
+      </c>
+      <c r="G916" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H916" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I916" s="41">
+        <v>0</v>
+      </c>
+      <c r="J916" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="917" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A917" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B917" s="11">
+        <v>4</v>
+      </c>
+      <c r="C917" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="D917" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Женя Одушкин</v>
+      </c>
+      <c r="E917" s="11">
+        <v>0</v>
+      </c>
+      <c r="F917" s="11">
+        <v>0</v>
+      </c>
+      <c r="G917" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H917" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I917" s="41">
+        <v>0</v>
+      </c>
+      <c r="J917" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="918" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A918" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B918" s="11">
+        <v>2</v>
+      </c>
+      <c r="C918" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D918" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Богдан Ждамаров</v>
+      </c>
+      <c r="E918" s="11">
+        <v>0</v>
+      </c>
+      <c r="F918" s="11">
+        <v>0</v>
+      </c>
+      <c r="G918" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H918" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I918" s="41">
+        <v>1</v>
+      </c>
+      <c r="J918" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="919" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A919" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B919" s="11">
+        <v>4</v>
+      </c>
+      <c r="C919" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="D919" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Юра Пименов</v>
+      </c>
+      <c r="E919" s="11">
+        <v>1</v>
+      </c>
+      <c r="F919" s="11">
+        <v>1</v>
+      </c>
+      <c r="G919" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H919" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I919" s="41">
+        <v>0</v>
+      </c>
+      <c r="J919" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="920" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A920" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B920" s="11">
+        <v>1</v>
+      </c>
+      <c r="C920" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="D920" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Арги</v>
+      </c>
+      <c r="E920" s="11">
+        <v>2</v>
+      </c>
+      <c r="F920" s="11">
+        <v>3</v>
+      </c>
+      <c r="G920" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H920" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I920" s="41">
+        <v>0</v>
+      </c>
+      <c r="J920" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="921" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A921" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B921" s="11">
+        <v>3</v>
+      </c>
+      <c r="C921" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="D921" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Андрей (АК+1)</v>
+      </c>
+      <c r="E921" s="11">
+        <v>2</v>
+      </c>
+      <c r="F921" s="11">
+        <v>0</v>
+      </c>
+      <c r="G921" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H921" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I921" s="41">
+        <v>0</v>
+      </c>
+      <c r="J921" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="922" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A922" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B922" s="11">
+        <v>1</v>
+      </c>
+      <c r="C922" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="D922" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Олег Шишкин</v>
+      </c>
+      <c r="E922" s="11">
+        <v>2</v>
+      </c>
+      <c r="F922" s="11">
+        <v>1</v>
+      </c>
+      <c r="G922" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H922" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I922" s="41">
+        <v>0</v>
+      </c>
+      <c r="J922" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="923" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A923" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B923" s="11">
+        <v>3</v>
+      </c>
+      <c r="C923" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="D923" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Миша</v>
+      </c>
+      <c r="E923" s="11">
+        <v>0</v>
+      </c>
+      <c r="F923" s="11">
+        <v>0</v>
+      </c>
+      <c r="G923" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H923" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I923" s="41">
+        <v>0</v>
+      </c>
+      <c r="J923" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="924" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A924" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B924" s="11">
+        <v>3</v>
+      </c>
+      <c r="C924" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="D924" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Эля</v>
+      </c>
+      <c r="E924" s="11">
+        <v>0</v>
+      </c>
+      <c r="F924" s="11">
+        <v>0</v>
+      </c>
+      <c r="G924" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H924" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I924" s="41">
+        <v>0</v>
+      </c>
+      <c r="J924" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="925" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A925" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B925" s="11">
+        <v>2</v>
+      </c>
+      <c r="C925" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="D925" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Дима Сахаров</v>
+      </c>
+      <c r="E925" s="11">
+        <v>1</v>
+      </c>
+      <c r="F925" s="11">
+        <v>0</v>
+      </c>
+      <c r="G925" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H925" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I925" s="41">
+        <v>0</v>
+      </c>
+      <c r="J925" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="926" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A926" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B926" s="11">
+        <v>1</v>
+      </c>
+      <c r="C926" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="D926" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Анашкин</v>
+      </c>
+      <c r="E926" s="11">
+        <v>2</v>
+      </c>
+      <c r="F926" s="11">
+        <v>1</v>
+      </c>
+      <c r="G926" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H926" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I926" s="41">
+        <v>0</v>
+      </c>
+      <c r="J926" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="927" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A927" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B927" s="11">
+        <v>3</v>
+      </c>
+      <c r="C927" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="D927" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Женя (кипер)</v>
+      </c>
+      <c r="E927" s="11">
+        <v>0</v>
+      </c>
+      <c r="F927" s="11">
+        <v>0</v>
+      </c>
+      <c r="G927" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H927" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I927" s="41">
+        <v>0</v>
+      </c>
+      <c r="J927" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="928" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A928" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B928" s="11">
+        <v>4</v>
+      </c>
+      <c r="C928" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="D928" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Никита</v>
+      </c>
+      <c r="E928" s="11">
+        <v>0</v>
+      </c>
+      <c r="F928" s="11">
+        <v>0</v>
+      </c>
+      <c r="G928" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H928" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I928" s="41">
+        <v>0</v>
+      </c>
+      <c r="J928" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="929" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A929" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B929" s="11">
+        <v>2</v>
+      </c>
+      <c r="C929" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="D929" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей Крюков</v>
+      </c>
+      <c r="E929" s="11">
+        <v>0</v>
+      </c>
+      <c r="F929" s="11">
+        <v>0</v>
+      </c>
+      <c r="G929" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H929" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I929" s="41">
+        <v>0</v>
+      </c>
+      <c r="J929" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="930" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A930" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B930" s="11">
+        <v>2</v>
+      </c>
+      <c r="C930" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="D930" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Зинаддин Алимов</v>
+      </c>
+      <c r="E930" s="11">
+        <v>1</v>
+      </c>
+      <c r="F930" s="11">
+        <v>0</v>
+      </c>
+      <c r="G930" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H930" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I930" s="41">
+        <v>0</v>
+      </c>
+      <c r="J930" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="931" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A931" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B931" s="11">
+        <v>4</v>
+      </c>
+      <c r="C931" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="D931" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей</v>
+      </c>
+      <c r="E931" s="11">
+        <v>0</v>
+      </c>
+      <c r="F931" s="11">
+        <v>0</v>
+      </c>
+      <c r="G931" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H931" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I931" s="41">
+        <v>0</v>
+      </c>
+      <c r="J931" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="932" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A932" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B932" s="11">
+        <v>1</v>
+      </c>
+      <c r="C932" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D932" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Толя Шлаев</v>
+      </c>
+      <c r="E932" s="11">
+        <v>1</v>
+      </c>
+      <c r="F932" s="11">
+        <v>0</v>
+      </c>
+      <c r="G932" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H932" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I932" s="41">
+        <v>0</v>
+      </c>
+      <c r="J932" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="933" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A933" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B933" s="11">
+        <v>4</v>
+      </c>
+      <c r="C933" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="D933" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Игорь Фомичев</v>
+      </c>
+      <c r="E933" s="11">
+        <v>0</v>
+      </c>
+      <c r="F933" s="11">
+        <v>1</v>
+      </c>
+      <c r="G933" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H933" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I933" s="41">
+        <v>0</v>
+      </c>
+      <c r="J933" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="934" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A934" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B934" s="11">
+        <v>3</v>
+      </c>
+      <c r="C934" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="D934" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Илья (АК+1)</v>
+      </c>
+      <c r="E934" s="11">
+        <v>0</v>
+      </c>
+      <c r="F934" s="11">
+        <v>0</v>
+      </c>
+      <c r="G934" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H934" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I934" s="41">
+        <v>0</v>
+      </c>
+      <c r="J934" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="935" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A935" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B935" s="11">
+        <v>3</v>
+      </c>
+      <c r="C935" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="D935" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Кирилл (АК+1)</v>
+      </c>
+      <c r="E935" s="11">
+        <v>0</v>
+      </c>
+      <c r="F935" s="11">
+        <v>0</v>
+      </c>
+      <c r="G935" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H935" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I935" s="41">
+        <v>0</v>
+      </c>
+      <c r="J935" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="936" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A936" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B936" s="11">
+        <v>4</v>
+      </c>
+      <c r="C936" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="D936" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Рома Сурнин</v>
+      </c>
+      <c r="E936" s="11">
+        <v>2</v>
+      </c>
+      <c r="F936" s="11">
+        <v>0</v>
+      </c>
+      <c r="G936" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H936" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I936" s="41">
+        <v>0</v>
+      </c>
+      <c r="J936" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="937" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A937" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B937" s="11">
+        <v>1</v>
+      </c>
+      <c r="C937" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="D937" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Рыжий</v>
+      </c>
+      <c r="E937" s="11">
+        <v>0</v>
+      </c>
+      <c r="F937" s="11">
+        <v>0</v>
+      </c>
+      <c r="G937" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H937" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I937" s="41">
+        <v>0</v>
+      </c>
+      <c r="J937" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="938" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A938" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B938" s="11">
+        <v>1</v>
+      </c>
+      <c r="C938" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="D938" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Рус (Рыжий +1)</v>
+      </c>
+      <c r="E938" s="11">
+        <v>3</v>
+      </c>
+      <c r="F938" s="11">
+        <v>1</v>
+      </c>
+      <c r="G938" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H938" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I938" s="41">
+        <v>0</v>
+      </c>
+      <c r="J938" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="939" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A939" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B939" s="11">
+        <v>2</v>
+      </c>
+      <c r="C939" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D939" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Ден (Зидан +1)</v>
+      </c>
+      <c r="E939" s="11">
+        <v>0</v>
+      </c>
+      <c r="F939" s="11">
+        <v>0</v>
+      </c>
+      <c r="G939" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H939" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I939" s="41">
+        <v>0</v>
+      </c>
+      <c r="J939" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="940" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A940" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B940" s="11">
+        <v>2</v>
+      </c>
+      <c r="C940" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D940" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Эльдар</v>
+      </c>
+      <c r="E940" s="11">
+        <v>0</v>
+      </c>
+      <c r="F940" s="11">
+        <v>1</v>
+      </c>
+      <c r="G940" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H940" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I940" s="41">
+        <v>1</v>
+      </c>
+      <c r="J940" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="941" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A941" s="23">
+        <v>46110</v>
+      </c>
+      <c r="B941" s="11">
+        <v>2</v>
+      </c>
+      <c r="C941" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="D941" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Назар (Женя +1)</v>
+      </c>
+      <c r="E941" s="11">
+        <v>0</v>
+      </c>
+      <c r="F941" s="11">
+        <v>0</v>
+      </c>
+      <c r="G941" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H941" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I941" s="41">
+        <v>0</v>
+      </c>
+      <c r="J941" s="16" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -36959,7 +38019,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E137"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -39229,9 +40289,77 @@
         <v>105</v>
       </c>
     </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="13">
+        <v>46110</v>
+      </c>
+      <c r="B134" s="7">
+        <v>1</v>
+      </c>
+      <c r="C134" s="8">
+        <v>6</v>
+      </c>
+      <c r="D134" s="8">
+        <v>0</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="13">
+        <v>46110</v>
+      </c>
+      <c r="B135" s="7">
+        <v>2</v>
+      </c>
+      <c r="C135" s="8">
+        <v>1</v>
+      </c>
+      <c r="D135" s="8">
+        <v>0</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="13">
+        <v>46110</v>
+      </c>
+      <c r="B136" s="7">
+        <v>3</v>
+      </c>
+      <c r="C136" s="8">
+        <v>2</v>
+      </c>
+      <c r="D136" s="8">
+        <v>0</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="13">
+        <v>46110</v>
+      </c>
+      <c r="B137" s="7">
+        <v>4</v>
+      </c>
+      <c r="C137" s="8">
+        <v>1</v>
+      </c>
+      <c r="D137" s="8">
+        <v>0</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B133" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B137" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>

--- a/football_stats.xlsx
+++ b/football_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\football_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01754BC2-ED51-4782-A5B4-816504F354F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD532B5A-EC7F-42F9-B7DA-4728163DC39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37086,7 +37086,7 @@
         <v>0</v>
       </c>
       <c r="J915" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="916" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37121,7 +37121,7 @@
         <v>0</v>
       </c>
       <c r="J916" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="917" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37156,7 +37156,7 @@
         <v>0</v>
       </c>
       <c r="J917" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="918" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37191,7 +37191,7 @@
         <v>1</v>
       </c>
       <c r="J918" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="919" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37226,7 +37226,7 @@
         <v>0</v>
       </c>
       <c r="J919" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="920" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37261,7 +37261,7 @@
         <v>0</v>
       </c>
       <c r="J920" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="921" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37296,7 +37296,7 @@
         <v>0</v>
       </c>
       <c r="J921" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="922" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37331,7 +37331,7 @@
         <v>0</v>
       </c>
       <c r="J922" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="923" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37366,7 +37366,7 @@
         <v>0</v>
       </c>
       <c r="J923" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="924" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37401,7 +37401,7 @@
         <v>0</v>
       </c>
       <c r="J924" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="925" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37436,7 +37436,7 @@
         <v>0</v>
       </c>
       <c r="J925" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="926" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37471,7 +37471,7 @@
         <v>0</v>
       </c>
       <c r="J926" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="927" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37506,7 +37506,7 @@
         <v>0</v>
       </c>
       <c r="J927" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="928" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37541,7 +37541,7 @@
         <v>0</v>
       </c>
       <c r="J928" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="929" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37576,7 +37576,7 @@
         <v>0</v>
       </c>
       <c r="J929" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="930" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37611,7 +37611,7 @@
         <v>0</v>
       </c>
       <c r="J930" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="931" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37646,7 +37646,7 @@
         <v>0</v>
       </c>
       <c r="J931" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="932" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37681,7 +37681,7 @@
         <v>0</v>
       </c>
       <c r="J932" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="933" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37716,7 +37716,7 @@
         <v>0</v>
       </c>
       <c r="J933" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="934" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37751,7 +37751,7 @@
         <v>0</v>
       </c>
       <c r="J934" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="935" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37786,7 +37786,7 @@
         <v>0</v>
       </c>
       <c r="J935" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="936" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37821,7 +37821,7 @@
         <v>0</v>
       </c>
       <c r="J936" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="937" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37856,7 +37856,7 @@
         <v>0</v>
       </c>
       <c r="J937" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="938" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37891,7 +37891,7 @@
         <v>0</v>
       </c>
       <c r="J938" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="939" spans="1:10" x14ac:dyDescent="0.25">
@@ -37926,7 +37926,7 @@
         <v>0</v>
       </c>
       <c r="J939" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="940" spans="1:10" x14ac:dyDescent="0.25">
@@ -37961,7 +37961,7 @@
         <v>1</v>
       </c>
       <c r="J940" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="941" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -37996,7 +37996,7 @@
         <v>0</v>
       </c>
       <c r="J941" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -40303,7 +40303,7 @@
         <v>0</v>
       </c>
       <c r="E134" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -40320,7 +40320,7 @@
         <v>0</v>
       </c>
       <c r="E135" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -40337,7 +40337,7 @@
         <v>0</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -40354,7 +40354,7 @@
         <v>0</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/football_stats.xlsx
+++ b/football_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\football_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD532B5A-EC7F-42F9-B7DA-4728163DC39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9886194C-6D96-4418-ADA3-DDBC7C494D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2276" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2335" uniqueCount="140">
   <si>
     <t>player_id</t>
   </si>
@@ -467,6 +467,15 @@
   <si>
     <t>Арги</t>
   </si>
+  <si>
+    <t>Макс Логинов</t>
+  </si>
+  <si>
+    <t>Семен (АК+1)</t>
+  </si>
+  <si>
+    <t>Ернур</t>
+  </si>
 </sst>
 </file>
 
@@ -666,7 +675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -791,6 +800,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -900,6 +912,13 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -917,13 +936,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1339,8 +1351,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G120" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
-  <autoFilter ref="A1:G120" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G123" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
+  <autoFilter ref="A1:G123" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G74">
     <sortCondition descending="1" ref="G1:G74"/>
   </sortState>
@@ -1368,8 +1380,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J941" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A1:J941" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J966" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:J966" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G60">
     <sortCondition ref="A1:A60"/>
   </sortState>
@@ -1396,8 +1408,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E137" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E137" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E140" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E140" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{92BE0DCE-EF0C-43B2-937D-640EBFF087A6}" name="date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{B497FB59-180E-4B72-9ECD-E25C88173489}" name="team_number" dataDxfId="3"/>
@@ -1675,7 +1687,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" style="38" bestFit="1" customWidth="1"/>
@@ -1775,7 +1787,7 @@
       </c>
       <c r="C4" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D4" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1783,15 +1795,15 @@
       </c>
       <c r="E4" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F4" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G4" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>280</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1831,7 +1843,7 @@
       </c>
       <c r="C6" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1839,15 +1851,15 @@
       </c>
       <c r="E6" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F6" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G6" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>209</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1891,19 +1903,19 @@
       </c>
       <c r="D8" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F8" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G8" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2007,15 +2019,15 @@
       </c>
       <c r="E12" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F12" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G12" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2063,15 +2075,15 @@
       </c>
       <c r="E14" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F14" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G14" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2143,19 +2155,19 @@
       </c>
       <c r="D17" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F17" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G17" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2227,19 +2239,19 @@
       </c>
       <c r="D20" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F20" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G20" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2251,23 +2263,23 @@
       </c>
       <c r="C21" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D21" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E21" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F21" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G21" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2279,7 +2291,7 @@
       </c>
       <c r="C22" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2287,15 +2299,15 @@
       </c>
       <c r="E22" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F22" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G22" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2371,15 +2383,15 @@
       </c>
       <c r="E25" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F25" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G25" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2395,19 +2407,19 @@
       </c>
       <c r="D26" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F26" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G26" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2559,23 +2571,23 @@
       </c>
       <c r="C32" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D32" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E32" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F32" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G32" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2651,15 +2663,15 @@
       </c>
       <c r="E35" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F35" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G35" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2699,7 +2711,7 @@
       </c>
       <c r="C37" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2707,15 +2719,15 @@
       </c>
       <c r="E37" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F37" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G37" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2763,15 +2775,15 @@
       </c>
       <c r="E39" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F39" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G39" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2811,7 +2823,7 @@
       </c>
       <c r="C41" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D41" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2819,15 +2831,15 @@
       </c>
       <c r="E41" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F41" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G41" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2839,23 +2851,23 @@
       </c>
       <c r="C42" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D42" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E42" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F42" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G42" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2871,19 +2883,19 @@
       </c>
       <c r="D43" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E43" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F43" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G43" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3211,15 +3223,15 @@
       </c>
       <c r="E55" s="7">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F55" s="8">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G55" s="8">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3459,19 +3471,19 @@
       </c>
       <c r="D64" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E64" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F64" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G64" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3791,23 +3803,23 @@
       </c>
       <c r="C76" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D76" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E76" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F76" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G76" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>89</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -5031,15 +5043,99 @@
       </c>
       <c r="E120" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F120" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G120" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>11</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A121" s="42" t="s">
+        <v>137</v>
+      </c>
+      <c r="B121" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="C121" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>2</v>
+      </c>
+      <c r="D121" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="E121" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>3</v>
+      </c>
+      <c r="F121" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>3</v>
+      </c>
+      <c r="G121" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A122" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="B122" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="C122" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D122" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E122" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>2</v>
+      </c>
+      <c r="F122" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>4</v>
+      </c>
+      <c r="G122" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A123" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="B123" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="C123" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D123" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E123" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>2</v>
+      </c>
+      <c r="F123" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>4</v>
+      </c>
+      <c r="G123" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5055,7 +5151,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:J941"/>
+  <dimension ref="A1:J966"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -37996,6 +38092,881 @@
         <v>0</v>
       </c>
       <c r="J941" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="942" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A942" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B942" s="11">
+        <v>2</v>
+      </c>
+      <c r="C942" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="D942" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Андрей (АК+1)</v>
+      </c>
+      <c r="E942" s="11">
+        <v>0</v>
+      </c>
+      <c r="F942" s="11">
+        <v>1</v>
+      </c>
+      <c r="G942" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H942" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="I942" s="41">
+        <v>0</v>
+      </c>
+      <c r="J942" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="943" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A943" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B943" s="11">
+        <v>2</v>
+      </c>
+      <c r="C943" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="D943" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Атай</v>
+      </c>
+      <c r="E943" s="11">
+        <v>0</v>
+      </c>
+      <c r="F943" s="11">
+        <v>1</v>
+      </c>
+      <c r="G943" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H943" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="I943" s="41">
+        <v>0</v>
+      </c>
+      <c r="J943" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="944" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A944" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B944" s="11">
+        <v>3</v>
+      </c>
+      <c r="C944" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="D944" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Семен (АК+1)</v>
+      </c>
+      <c r="E944" s="11">
+        <v>0</v>
+      </c>
+      <c r="F944" s="11">
+        <v>0</v>
+      </c>
+      <c r="G944" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H944" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="I944" s="41">
+        <v>0</v>
+      </c>
+      <c r="J944" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="945" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A945" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B945" s="11">
+        <v>3</v>
+      </c>
+      <c r="C945" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="D945" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Юра Пименов</v>
+      </c>
+      <c r="E945" s="11">
+        <v>0</v>
+      </c>
+      <c r="F945" s="11">
+        <v>0</v>
+      </c>
+      <c r="G945" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H945" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="I945" s="41">
+        <v>0</v>
+      </c>
+      <c r="J945" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="946" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A946" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B946" s="11">
+        <v>2</v>
+      </c>
+      <c r="C946" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D946" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Нурик</v>
+      </c>
+      <c r="E946" s="11">
+        <v>0</v>
+      </c>
+      <c r="F946" s="11">
+        <v>1</v>
+      </c>
+      <c r="G946" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H946" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="I946" s="41">
+        <v>0</v>
+      </c>
+      <c r="J946" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="947" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A947" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B947" s="11">
+        <v>3</v>
+      </c>
+      <c r="C947" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="D947" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Арги</v>
+      </c>
+      <c r="E947" s="11">
+        <v>0</v>
+      </c>
+      <c r="F947" s="11">
+        <v>0</v>
+      </c>
+      <c r="G947" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H947" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="I947" s="41">
+        <v>0</v>
+      </c>
+      <c r="J947" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="948" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A948" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B948" s="11">
+        <v>1</v>
+      </c>
+      <c r="C948" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="D948" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Эля</v>
+      </c>
+      <c r="E948" s="11">
+        <v>0</v>
+      </c>
+      <c r="F948" s="11">
+        <v>1</v>
+      </c>
+      <c r="G948" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H948" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="I948" s="41">
+        <v>0</v>
+      </c>
+      <c r="J948" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="949" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A949" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B949" s="11">
+        <v>1</v>
+      </c>
+      <c r="C949" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="D949" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Женя (кипер)</v>
+      </c>
+      <c r="E949" s="11">
+        <v>0</v>
+      </c>
+      <c r="F949" s="11">
+        <v>0</v>
+      </c>
+      <c r="G949" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H949" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="I949" s="41">
+        <v>3</v>
+      </c>
+      <c r="J949" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="950" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A950" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B950" s="11">
+        <v>3</v>
+      </c>
+      <c r="C950" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="D950" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Ернур</v>
+      </c>
+      <c r="E950" s="11">
+        <v>0</v>
+      </c>
+      <c r="F950" s="11">
+        <v>0</v>
+      </c>
+      <c r="G950" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H950" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="I950" s="41">
+        <v>3</v>
+      </c>
+      <c r="J950" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="951" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A951" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B951" s="11">
+        <v>3</v>
+      </c>
+      <c r="C951" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="D951" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Дима Сахаров</v>
+      </c>
+      <c r="E951" s="11">
+        <v>1</v>
+      </c>
+      <c r="F951" s="11">
+        <v>1</v>
+      </c>
+      <c r="G951" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H951" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="I951" s="41">
+        <v>0</v>
+      </c>
+      <c r="J951" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="952" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A952" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B952" s="11">
+        <v>3</v>
+      </c>
+      <c r="C952" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="D952" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Игорь Фомичев</v>
+      </c>
+      <c r="E952" s="11">
+        <v>3</v>
+      </c>
+      <c r="F952" s="11">
+        <v>1</v>
+      </c>
+      <c r="G952" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H952" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="I952" s="41">
+        <v>0</v>
+      </c>
+      <c r="J952" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="953" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A953" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B953" s="11">
+        <v>1</v>
+      </c>
+      <c r="C953" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="D953" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Анашкин</v>
+      </c>
+      <c r="E953" s="11">
+        <v>0</v>
+      </c>
+      <c r="F953" s="11">
+        <v>2</v>
+      </c>
+      <c r="G953" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H953" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="I953" s="41">
+        <v>0</v>
+      </c>
+      <c r="J953" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="954" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A954" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B954" s="11">
+        <v>2</v>
+      </c>
+      <c r="C954" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="D954" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Олег Шишкин</v>
+      </c>
+      <c r="E954" s="11">
+        <v>0</v>
+      </c>
+      <c r="F954" s="11">
+        <v>0</v>
+      </c>
+      <c r="G954" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H954" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="I954" s="41">
+        <v>1</v>
+      </c>
+      <c r="J954" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="955" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A955" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B955" s="11">
+        <v>1</v>
+      </c>
+      <c r="C955" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="D955" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей</v>
+      </c>
+      <c r="E955" s="11">
+        <v>3</v>
+      </c>
+      <c r="F955" s="11">
+        <v>0</v>
+      </c>
+      <c r="G955" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H955" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="I955" s="41">
+        <v>0</v>
+      </c>
+      <c r="J955" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="956" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A956" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B956" s="11">
+        <v>2</v>
+      </c>
+      <c r="C956" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="D956" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей Крюков</v>
+      </c>
+      <c r="E956" s="11">
+        <v>2</v>
+      </c>
+      <c r="F956" s="11">
+        <v>0</v>
+      </c>
+      <c r="G956" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H956" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="I956" s="41">
+        <v>1</v>
+      </c>
+      <c r="J956" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="957" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A957" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B957" s="11">
+        <v>1</v>
+      </c>
+      <c r="C957" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D957" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Толя Шлаев</v>
+      </c>
+      <c r="E957" s="11">
+        <v>1</v>
+      </c>
+      <c r="F957" s="11">
+        <v>0</v>
+      </c>
+      <c r="G957" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H957" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="I957" s="41">
+        <v>0</v>
+      </c>
+      <c r="J957" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="958" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A958" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B958" s="11">
+        <v>1</v>
+      </c>
+      <c r="C958" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="D958" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Кирилл Попов</v>
+      </c>
+      <c r="E958" s="11">
+        <v>0</v>
+      </c>
+      <c r="F958" s="11">
+        <v>0</v>
+      </c>
+      <c r="G958" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H958" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="I958" s="41">
+        <v>0</v>
+      </c>
+      <c r="J958" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="959" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A959" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B959" s="11">
+        <v>3</v>
+      </c>
+      <c r="C959" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="D959" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Рома Сурнин</v>
+      </c>
+      <c r="E959" s="11">
+        <v>1</v>
+      </c>
+      <c r="F959" s="11">
+        <v>0</v>
+      </c>
+      <c r="G959" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H959" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="I959" s="41">
+        <v>0</v>
+      </c>
+      <c r="J959" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="960" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A960" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B960" s="11">
+        <v>2</v>
+      </c>
+      <c r="C960" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="D960" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Эльдар</v>
+      </c>
+      <c r="E960" s="11">
+        <v>0</v>
+      </c>
+      <c r="F960" s="11">
+        <v>0</v>
+      </c>
+      <c r="G960" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H960" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="I960" s="41">
+        <v>2</v>
+      </c>
+      <c r="J960" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="961" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A961" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B961" s="11">
+        <v>1</v>
+      </c>
+      <c r="C961" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D961" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Дядя Руслан</v>
+      </c>
+      <c r="E961" s="11">
+        <v>1</v>
+      </c>
+      <c r="F961" s="11">
+        <v>0</v>
+      </c>
+      <c r="G961" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H961" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="I961" s="41">
+        <v>0</v>
+      </c>
+      <c r="J961" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="962" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A962" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B962" s="11">
+        <v>2</v>
+      </c>
+      <c r="C962" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="D962" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Игорь (Ник +1)</v>
+      </c>
+      <c r="E962" s="11">
+        <v>0</v>
+      </c>
+      <c r="F962" s="11">
+        <v>0</v>
+      </c>
+      <c r="G962" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H962" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="I962" s="41">
+        <v>0</v>
+      </c>
+      <c r="J962" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="963" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A963" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B963" s="11">
+        <v>2</v>
+      </c>
+      <c r="C963" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D963" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Расул</v>
+      </c>
+      <c r="E963" s="11">
+        <v>0</v>
+      </c>
+      <c r="F963" s="11">
+        <v>1</v>
+      </c>
+      <c r="G963" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H963" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="I963" s="41">
+        <v>0</v>
+      </c>
+      <c r="J963" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="964" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A964" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B964" s="11">
+        <v>3</v>
+      </c>
+      <c r="C964" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="D964" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Женя Одушкин</v>
+      </c>
+      <c r="E964" s="11">
+        <v>1</v>
+      </c>
+      <c r="F964" s="11">
+        <v>1</v>
+      </c>
+      <c r="G964" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H964" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="I964" s="41">
+        <v>0</v>
+      </c>
+      <c r="J964" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="965" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A965" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B965" s="11">
+        <v>1</v>
+      </c>
+      <c r="C965" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="D965" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Макс Логинов</v>
+      </c>
+      <c r="E965" s="11">
+        <v>2</v>
+      </c>
+      <c r="F965" s="11">
+        <v>1</v>
+      </c>
+      <c r="G965" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H965" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="I965" s="41">
+        <v>0</v>
+      </c>
+      <c r="J965" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="966" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A966" s="23">
+        <v>46117</v>
+      </c>
+      <c r="B966" s="11">
+        <v>2</v>
+      </c>
+      <c r="C966" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="D966" s="16" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Зинаддин Алимов</v>
+      </c>
+      <c r="E966" s="11">
+        <v>5</v>
+      </c>
+      <c r="F966" s="11">
+        <v>1</v>
+      </c>
+      <c r="G966" s="16">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H966" s="16">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="I966" s="41">
+        <v>0</v>
+      </c>
+      <c r="J966" s="16" t="s">
         <v>105</v>
       </c>
     </row>
@@ -38019,7 +38990,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -40357,9 +41328,60 @@
         <v>105</v>
       </c>
     </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="13">
+        <v>46117</v>
+      </c>
+      <c r="B138" s="7">
+        <v>1</v>
+      </c>
+      <c r="C138" s="8">
+        <v>3</v>
+      </c>
+      <c r="D138" s="8">
+        <v>3</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="13">
+        <v>46117</v>
+      </c>
+      <c r="B139" s="7">
+        <v>2</v>
+      </c>
+      <c r="C139" s="8">
+        <v>3</v>
+      </c>
+      <c r="D139" s="8">
+        <v>5</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="13">
+        <v>46117</v>
+      </c>
+      <c r="B140" s="7">
+        <v>3</v>
+      </c>
+      <c r="C140" s="8">
+        <v>2</v>
+      </c>
+      <c r="D140" s="8">
+        <v>4</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B137" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B140" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>

--- a/football_stats.xlsx
+++ b/football_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\football_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9886194C-6D96-4418-ADA3-DDBC7C494D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0DE0B6C-BC62-4A22-93EE-585F12B1E26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2335" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="144">
   <si>
     <t>player_id</t>
   </si>
@@ -476,6 +476,18 @@
   <si>
     <t>Ернур</t>
   </si>
+  <si>
+    <t>Энрике (Энтони+1)</t>
+  </si>
+  <si>
+    <t>Хамзат (Расул+1)</t>
+  </si>
+  <si>
+    <t>Коля (АК+1)</t>
+  </si>
+  <si>
+    <t>Еренур</t>
+  </si>
 </sst>
 </file>
 
@@ -534,6 +546,8 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -912,13 +926,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -936,6 +943,13 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1351,8 +1365,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G123" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
-  <autoFilter ref="A1:G123" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G126" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
+  <autoFilter ref="A1:G126" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G74">
     <sortCondition descending="1" ref="G1:G74"/>
   </sortState>
@@ -1380,8 +1394,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J966" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A1:J966" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J999" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:J999" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G60">
     <sortCondition ref="A1:A60"/>
   </sortState>
@@ -1408,8 +1422,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E140" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E140" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E144" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E144" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{92BE0DCE-EF0C-43B2-937D-640EBFF087A6}" name="date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{B497FB59-180E-4B72-9ECD-E25C88173489}" name="team_number" dataDxfId="3"/>
@@ -1687,7 +1701,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" style="38" bestFit="1" customWidth="1"/>
@@ -1731,23 +1745,23 @@
       </c>
       <c r="C2" s="19">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D2" s="19">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="19">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F2" s="20">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" s="20">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>183</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1795,15 +1809,15 @@
       </c>
       <c r="E4" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F4" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G4" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1843,7 +1857,7 @@
       </c>
       <c r="C6" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1851,15 +1865,15 @@
       </c>
       <c r="E6" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F6" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1907,15 +1921,15 @@
       </c>
       <c r="E8" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F8" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G8" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1983,23 +1997,23 @@
       </c>
       <c r="C11" s="21">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D11" s="21">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E11" s="21">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F11" s="22">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G11" s="22">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2011,23 +2025,23 @@
       </c>
       <c r="C12" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D12" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E12" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F12" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G12" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>223</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2075,15 +2089,15 @@
       </c>
       <c r="E14" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F14" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G14" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2095,7 +2109,7 @@
       </c>
       <c r="C15" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2103,15 +2117,15 @@
       </c>
       <c r="E15" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F15" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2127,19 +2141,19 @@
       </c>
       <c r="D16" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F16" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2159,15 +2173,15 @@
       </c>
       <c r="E17" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F17" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2235,7 +2249,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D20" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2243,15 +2257,15 @@
       </c>
       <c r="E20" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F20" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2319,7 +2333,7 @@
       </c>
       <c r="C23" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2327,15 +2341,15 @@
       </c>
       <c r="E23" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F23" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G23" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2407,19 +2421,19 @@
       </c>
       <c r="D26" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E26" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F26" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G26" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2467,15 +2481,15 @@
       </c>
       <c r="E28" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F28" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G28" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2515,7 +2529,7 @@
       </c>
       <c r="C30" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2523,15 +2537,15 @@
       </c>
       <c r="E30" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F30" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2579,15 +2593,15 @@
       </c>
       <c r="E32" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F32" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G32" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2663,15 +2677,15 @@
       </c>
       <c r="E35" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F35" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G35" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2719,15 +2733,15 @@
       </c>
       <c r="E37" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F37" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G37" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2739,23 +2753,23 @@
       </c>
       <c r="C38" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D38" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E38" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F38" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G38" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>85</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2775,15 +2789,15 @@
       </c>
       <c r="E39" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F39" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G39" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2823,23 +2837,23 @@
       </c>
       <c r="C41" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D41" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E41" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F41" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G41" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3467,23 +3481,23 @@
       </c>
       <c r="C64" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D64" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E64" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F64" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G64" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3887,23 +3901,23 @@
       </c>
       <c r="C79" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D79" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E79" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F79" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G79" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3999,23 +4013,23 @@
       </c>
       <c r="C83" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D83" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E83" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F83" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G83" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -4115,19 +4129,19 @@
       </c>
       <c r="D87" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E87" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F87" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G87" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4287,15 +4301,15 @@
       </c>
       <c r="E93" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F93" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G93" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -4643,23 +4657,23 @@
       </c>
       <c r="C106" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D106" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F106" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G106" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4763,15 +4777,15 @@
       </c>
       <c r="E110" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F110" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G110" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5035,23 +5049,23 @@
       </c>
       <c r="C120" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D120" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E120" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F120" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G120" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5136,6 +5150,90 @@
       <c r="G123" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
         <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="B124" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="C124" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D124" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E124" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>3</v>
+      </c>
+      <c r="F124" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="G124" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="B125" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="C125" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D125" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E125" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>3</v>
+      </c>
+      <c r="F125" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="G125" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="B126" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="C126" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>3</v>
+      </c>
+      <c r="D126" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="E126" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>3</v>
+      </c>
+      <c r="F126" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="G126" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5151,7 +5249,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:J966"/>
+  <dimension ref="A1:J999"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -38967,6 +39065,1161 @@
         <v>0</v>
       </c>
       <c r="J966" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="967" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A967" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B967" s="7">
+        <v>2</v>
+      </c>
+      <c r="C967" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D967" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Артем Ширяев</v>
+      </c>
+      <c r="E967" s="7">
+        <v>0</v>
+      </c>
+      <c r="F967" s="8">
+        <v>0</v>
+      </c>
+      <c r="G967" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H967" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I967" s="10">
+        <v>0</v>
+      </c>
+      <c r="J967" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="968" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A968" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B968" s="7">
+        <v>1</v>
+      </c>
+      <c r="C968" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D968" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Миша Орехов</v>
+      </c>
+      <c r="E968" s="7">
+        <v>1</v>
+      </c>
+      <c r="F968" s="8">
+        <v>1</v>
+      </c>
+      <c r="G968" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H968" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I968" s="10">
+        <v>0</v>
+      </c>
+      <c r="J968" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="969" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A969" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B969" s="7">
+        <v>1</v>
+      </c>
+      <c r="C969" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D969" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Максим Строцкий</v>
+      </c>
+      <c r="E969" s="7">
+        <v>0</v>
+      </c>
+      <c r="F969" s="8">
+        <v>1</v>
+      </c>
+      <c r="G969" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H969" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I969" s="10">
+        <v>1</v>
+      </c>
+      <c r="J969" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="970" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A970" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B970" s="7">
+        <v>4</v>
+      </c>
+      <c r="C970" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D970" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Атай</v>
+      </c>
+      <c r="E970" s="7">
+        <v>1</v>
+      </c>
+      <c r="F970" s="8">
+        <v>0</v>
+      </c>
+      <c r="G970" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H970" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I970" s="10">
+        <v>0</v>
+      </c>
+      <c r="J970" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="971" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A971" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B971" s="7">
+        <v>3</v>
+      </c>
+      <c r="C971" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D971" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Витя</v>
+      </c>
+      <c r="E971" s="7">
+        <v>1</v>
+      </c>
+      <c r="F971" s="8">
+        <v>0</v>
+      </c>
+      <c r="G971" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H971" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I971" s="10">
+        <v>1</v>
+      </c>
+      <c r="J971" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="972" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A972" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B972" s="7">
+        <v>4</v>
+      </c>
+      <c r="C972" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D972" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Нурик</v>
+      </c>
+      <c r="E972" s="7">
+        <v>0</v>
+      </c>
+      <c r="F972" s="8">
+        <v>0</v>
+      </c>
+      <c r="G972" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H972" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I972" s="10">
+        <v>0</v>
+      </c>
+      <c r="J972" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="973" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A973" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B973" s="7">
+        <v>3</v>
+      </c>
+      <c r="C973" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D973" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Арги</v>
+      </c>
+      <c r="E973" s="7">
+        <v>1</v>
+      </c>
+      <c r="F973" s="8">
+        <v>1</v>
+      </c>
+      <c r="G973" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H973" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I973" s="10">
+        <v>0</v>
+      </c>
+      <c r="J973" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="974" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A974" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B974" s="7">
+        <v>1</v>
+      </c>
+      <c r="C974" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D974" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Паша</v>
+      </c>
+      <c r="E974" s="7">
+        <v>2</v>
+      </c>
+      <c r="F974" s="8">
+        <v>1</v>
+      </c>
+      <c r="G974" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H974" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I974" s="10">
+        <v>0</v>
+      </c>
+      <c r="J974" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="975" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A975" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B975" s="7">
+        <v>1</v>
+      </c>
+      <c r="C975" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D975" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Олег Шишкин</v>
+      </c>
+      <c r="E975" s="7">
+        <v>0</v>
+      </c>
+      <c r="F975" s="8">
+        <v>0</v>
+      </c>
+      <c r="G975" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H975" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I975" s="10">
+        <v>0</v>
+      </c>
+      <c r="J975" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="976" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A976" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B976" s="7">
+        <v>2</v>
+      </c>
+      <c r="C976" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D976" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Женя (кипер)</v>
+      </c>
+      <c r="E976" s="7">
+        <v>0</v>
+      </c>
+      <c r="F976" s="8">
+        <v>0</v>
+      </c>
+      <c r="G976" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H976" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I976" s="10">
+        <v>4</v>
+      </c>
+      <c r="J976" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="977" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A977" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B977" s="7">
+        <v>3</v>
+      </c>
+      <c r="C977" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D977" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Коля (АК+1)</v>
+      </c>
+      <c r="E977" s="7">
+        <v>3</v>
+      </c>
+      <c r="F977" s="8">
+        <v>1</v>
+      </c>
+      <c r="G977" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H977" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I977" s="10">
+        <v>0</v>
+      </c>
+      <c r="J977" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="978" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A978" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B978" s="7">
+        <v>1</v>
+      </c>
+      <c r="C978" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D978" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Юра Пименов</v>
+      </c>
+      <c r="E978" s="7">
+        <v>2</v>
+      </c>
+      <c r="F978" s="8">
+        <v>2</v>
+      </c>
+      <c r="G978" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H978" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I978" s="10">
+        <v>0</v>
+      </c>
+      <c r="J978" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="979" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A979" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B979" s="7">
+        <v>3</v>
+      </c>
+      <c r="C979" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D979" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Антон Копыч</v>
+      </c>
+      <c r="E979" s="7">
+        <v>1</v>
+      </c>
+      <c r="F979" s="8">
+        <v>3</v>
+      </c>
+      <c r="G979" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H979" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I979" s="10">
+        <v>0</v>
+      </c>
+      <c r="J979" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="980" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A980" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B980" s="7">
+        <v>4</v>
+      </c>
+      <c r="C980" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D980" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Эля</v>
+      </c>
+      <c r="E980" s="7">
+        <v>0</v>
+      </c>
+      <c r="F980" s="8">
+        <v>2</v>
+      </c>
+      <c r="G980" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H980" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I980" s="10">
+        <v>0</v>
+      </c>
+      <c r="J980" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="981" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A981" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B981" s="7">
+        <v>1</v>
+      </c>
+      <c r="C981" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D981" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Анашкин</v>
+      </c>
+      <c r="E981" s="7">
+        <v>1</v>
+      </c>
+      <c r="F981" s="8">
+        <v>1</v>
+      </c>
+      <c r="G981" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H981" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I981" s="10">
+        <v>0</v>
+      </c>
+      <c r="J981" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="982" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A982" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B982" s="7">
+        <v>2</v>
+      </c>
+      <c r="C982" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D982" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Никита</v>
+      </c>
+      <c r="E982" s="7">
+        <v>3</v>
+      </c>
+      <c r="F982" s="8">
+        <v>1</v>
+      </c>
+      <c r="G982" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H982" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I982" s="10">
+        <v>0</v>
+      </c>
+      <c r="J982" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="983" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A983" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B983" s="7">
+        <v>2</v>
+      </c>
+      <c r="C983" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D983" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Илшат</v>
+      </c>
+      <c r="E983" s="7">
+        <v>2</v>
+      </c>
+      <c r="F983" s="8">
+        <v>2</v>
+      </c>
+      <c r="G983" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H983" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I983" s="10">
+        <v>0</v>
+      </c>
+      <c r="J983" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="984" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A984" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B984" s="7">
+        <v>3</v>
+      </c>
+      <c r="C984" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D984" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Александр Костюнин</v>
+      </c>
+      <c r="E984" s="7">
+        <v>1</v>
+      </c>
+      <c r="F984" s="8">
+        <v>0</v>
+      </c>
+      <c r="G984" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H984" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I984" s="10">
+        <v>1</v>
+      </c>
+      <c r="J984" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="985" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A985" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B985" s="7">
+        <v>3</v>
+      </c>
+      <c r="C985" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D985" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей Крюков</v>
+      </c>
+      <c r="E985" s="7">
+        <v>1</v>
+      </c>
+      <c r="F985" s="8">
+        <v>0</v>
+      </c>
+      <c r="G985" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H985" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I985" s="10">
+        <v>0</v>
+      </c>
+      <c r="J985" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="986" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A986" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B986" s="7">
+        <v>4</v>
+      </c>
+      <c r="C986" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D986" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Расул</v>
+      </c>
+      <c r="E986" s="7">
+        <v>0</v>
+      </c>
+      <c r="F986" s="8">
+        <v>0</v>
+      </c>
+      <c r="G986" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H986" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I986" s="10">
+        <v>0</v>
+      </c>
+      <c r="J986" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="987" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A987" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B987" s="7">
+        <v>1</v>
+      </c>
+      <c r="C987" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D987" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Богдан Ждамаров</v>
+      </c>
+      <c r="E987" s="7">
+        <v>0</v>
+      </c>
+      <c r="F987" s="8">
+        <v>0</v>
+      </c>
+      <c r="G987" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H987" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I987" s="10">
+        <v>0</v>
+      </c>
+      <c r="J987" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="988" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A988" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B988" s="7">
+        <v>2</v>
+      </c>
+      <c r="C988" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D988" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Дима (Спартак)</v>
+      </c>
+      <c r="E988" s="7">
+        <v>1</v>
+      </c>
+      <c r="F988" s="8">
+        <v>1</v>
+      </c>
+      <c r="G988" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H988" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I988" s="10">
+        <v>0</v>
+      </c>
+      <c r="J988" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="989" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A989" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B989" s="7">
+        <v>2</v>
+      </c>
+      <c r="C989" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D989" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Женя Одушкин</v>
+      </c>
+      <c r="E989" s="7">
+        <v>0</v>
+      </c>
+      <c r="F989" s="8">
+        <v>0</v>
+      </c>
+      <c r="G989" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H989" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I989" s="10">
+        <v>0</v>
+      </c>
+      <c r="J989" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="990" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A990" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B990" s="7">
+        <v>2</v>
+      </c>
+      <c r="C990" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D990" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей</v>
+      </c>
+      <c r="E990" s="7">
+        <v>0</v>
+      </c>
+      <c r="F990" s="8">
+        <v>0</v>
+      </c>
+      <c r="G990" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H990" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I990" s="10">
+        <v>0</v>
+      </c>
+      <c r="J990" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="991" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A991" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B991" s="7">
+        <v>2</v>
+      </c>
+      <c r="C991" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D991" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Энтони Тепеев</v>
+      </c>
+      <c r="E991" s="7">
+        <v>0</v>
+      </c>
+      <c r="F991" s="8">
+        <v>1</v>
+      </c>
+      <c r="G991" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H991" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I991" s="10">
+        <v>0</v>
+      </c>
+      <c r="J991" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="992" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A992" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B992" s="7">
+        <v>3</v>
+      </c>
+      <c r="C992" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D992" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Дядя Руслан</v>
+      </c>
+      <c r="E992" s="7">
+        <v>0</v>
+      </c>
+      <c r="F992" s="8">
+        <v>0</v>
+      </c>
+      <c r="G992" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H992" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I992" s="10">
+        <v>1</v>
+      </c>
+      <c r="J992" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="993" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A993" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B993" s="7">
+        <v>1</v>
+      </c>
+      <c r="C993" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D993" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v/>
+      </c>
+      <c r="E993" s="7">
+        <v>0</v>
+      </c>
+      <c r="F993" s="8">
+        <v>0</v>
+      </c>
+      <c r="G993" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H993" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I993" s="10">
+        <v>6</v>
+      </c>
+      <c r="J993" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="994" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A994" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B994" s="7">
+        <v>3</v>
+      </c>
+      <c r="C994" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D994" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Саша (Витя+1)</v>
+      </c>
+      <c r="E994" s="7">
+        <v>0</v>
+      </c>
+      <c r="F994" s="8">
+        <v>0</v>
+      </c>
+      <c r="G994" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H994" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I994" s="10">
+        <v>0</v>
+      </c>
+      <c r="J994" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="995" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A995" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B995" s="7">
+        <v>4</v>
+      </c>
+      <c r="C995" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D995" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Рома Сурнин</v>
+      </c>
+      <c r="E995" s="7">
+        <v>2</v>
+      </c>
+      <c r="F995" s="8">
+        <v>1</v>
+      </c>
+      <c r="G995" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H995" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I995" s="10">
+        <v>0</v>
+      </c>
+      <c r="J995" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="996" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A996" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B996" s="7">
+        <v>4</v>
+      </c>
+      <c r="C996" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D996" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Эльдар</v>
+      </c>
+      <c r="E996" s="7">
+        <v>0</v>
+      </c>
+      <c r="F996" s="8">
+        <v>0</v>
+      </c>
+      <c r="G996" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H996" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I996" s="10">
+        <v>1</v>
+      </c>
+      <c r="J996" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="997" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A997" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B997" s="7">
+        <v>4</v>
+      </c>
+      <c r="C997" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D997" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Энрике (Энтони+1)</v>
+      </c>
+      <c r="E997" s="7">
+        <v>0</v>
+      </c>
+      <c r="F997" s="8">
+        <v>0</v>
+      </c>
+      <c r="G997" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H997" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I997" s="10">
+        <v>0</v>
+      </c>
+      <c r="J997" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="998" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A998" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B998" s="7">
+        <v>4</v>
+      </c>
+      <c r="C998" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D998" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Хамзат (Расул+1)</v>
+      </c>
+      <c r="E998" s="7">
+        <v>0</v>
+      </c>
+      <c r="F998" s="8">
+        <v>0</v>
+      </c>
+      <c r="G998" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H998" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I998" s="10">
+        <v>0</v>
+      </c>
+      <c r="J998" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="999" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A999" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B999" s="7">
+        <v>4</v>
+      </c>
+      <c r="C999" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D999" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Рубик</v>
+      </c>
+      <c r="E999" s="7">
+        <v>1</v>
+      </c>
+      <c r="F999" s="8">
+        <v>0</v>
+      </c>
+      <c r="G999" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H999" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I999" s="10">
+        <v>0</v>
+      </c>
+      <c r="J999" s="16" t="s">
         <v>105</v>
       </c>
     </row>
@@ -38990,7 +40243,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -41379,9 +42632,77 @@
         <v>105</v>
       </c>
     </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="13">
+        <v>46124</v>
+      </c>
+      <c r="B141" s="7">
+        <v>1</v>
+      </c>
+      <c r="C141" s="8">
+        <v>5</v>
+      </c>
+      <c r="D141" s="8">
+        <v>2</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="13">
+        <v>46124</v>
+      </c>
+      <c r="B142" s="7">
+        <v>2</v>
+      </c>
+      <c r="C142" s="8">
+        <v>3</v>
+      </c>
+      <c r="D142" s="8">
+        <v>2</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="13">
+        <v>46124</v>
+      </c>
+      <c r="B143" s="7">
+        <v>3</v>
+      </c>
+      <c r="C143" s="8">
+        <v>3</v>
+      </c>
+      <c r="D143" s="8">
+        <v>1</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="13">
+        <v>46124</v>
+      </c>
+      <c r="B144" s="7">
+        <v>4</v>
+      </c>
+      <c r="C144" s="8">
+        <v>3</v>
+      </c>
+      <c r="D144" s="8">
+        <v>1</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B140" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B144" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>

--- a/football_stats.xlsx
+++ b/football_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\football_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0DE0B6C-BC62-4A22-93EE-585F12B1E26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA11176-3786-4970-9030-798D4309E67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="143">
   <si>
     <t>player_id</t>
   </si>
@@ -484,9 +484,6 @@
   </si>
   <si>
     <t>Коля (АК+1)</t>
-  </si>
-  <si>
-    <t>Еренур</t>
   </si>
 </sst>
 </file>
@@ -5125,10 +5122,10 @@
       </c>
     </row>
     <row r="123" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A123" s="42" t="s">
+      <c r="A123" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="B123" s="39" t="s">
+      <c r="B123" s="26" t="s">
         <v>139</v>
       </c>
       <c r="C123" s="10">
@@ -5141,15 +5138,15 @@
       </c>
       <c r="E123" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F123" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G123" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -39986,11 +39983,11 @@
         <v>1</v>
       </c>
       <c r="C993" s="7" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D993" s="10" t="str">
         <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
-        <v/>
+        <v>Ернур</v>
       </c>
       <c r="E993" s="7">
         <v>0</v>

--- a/football_stats.xlsx
+++ b/football_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\football_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA11176-3786-4970-9030-798D4309E67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A52E60B-8F84-45C5-A96D-00A708F2E142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="145">
   <si>
     <t>player_id</t>
   </si>
@@ -484,6 +484,12 @@
   </si>
   <si>
     <t>Коля (АК+1)</t>
+  </si>
+  <si>
+    <t>Андрей Волошин (АК+1)</t>
+  </si>
+  <si>
+    <t>Саша (АК+1)</t>
   </si>
 </sst>
 </file>
@@ -1362,8 +1368,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G126" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
-  <autoFilter ref="A1:G126" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G128" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
+  <autoFilter ref="A1:G128" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G74">
     <sortCondition descending="1" ref="G1:G74"/>
   </sortState>
@@ -1391,8 +1397,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J999" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A1:J999" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J1022" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:J1022" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G60">
     <sortCondition ref="A1:A60"/>
   </sortState>
@@ -1419,8 +1425,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E144" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E144" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E147" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E147" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{92BE0DCE-EF0C-43B2-937D-640EBFF087A6}" name="date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{B497FB59-180E-4B72-9ECD-E25C88173489}" name="team_number" dataDxfId="3"/>
@@ -1698,7 +1704,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" style="38" bestFit="1" customWidth="1"/>
@@ -1742,7 +1748,7 @@
       </c>
       <c r="C2" s="19">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D2" s="19">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1750,15 +1756,15 @@
       </c>
       <c r="E2" s="19">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F2" s="20">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G2" s="20">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1778,15 +1784,15 @@
       </c>
       <c r="E3" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F3" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G3" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1826,23 +1832,23 @@
       </c>
       <c r="C5" s="21">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="21">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="21">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F5" s="22">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5" s="22">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1862,15 +1868,15 @@
       </c>
       <c r="E6" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F6" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G6" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1918,15 +1924,15 @@
       </c>
       <c r="E8" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F8" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G8" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2086,15 +2092,15 @@
       </c>
       <c r="E14" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F14" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G14" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2254,15 +2260,15 @@
       </c>
       <c r="E20" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F20" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G20" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2310,15 +2316,15 @@
       </c>
       <c r="E22" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F22" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G22" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2394,15 +2400,15 @@
       </c>
       <c r="E25" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F25" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G25" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2422,15 +2428,15 @@
       </c>
       <c r="E26" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F26" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G26" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2442,23 +2448,23 @@
       </c>
       <c r="C27" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D27" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E27" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F27" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G27" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2526,7 +2532,7 @@
       </c>
       <c r="C30" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2534,15 +2540,15 @@
       </c>
       <c r="E30" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F30" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G30" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2562,15 +2568,15 @@
       </c>
       <c r="E31" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F31" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2610,7 +2616,7 @@
       </c>
       <c r="C33" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D33" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2618,15 +2624,15 @@
       </c>
       <c r="E33" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F33" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G33" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2786,15 +2792,15 @@
       </c>
       <c r="E39" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F39" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G39" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2894,19 +2900,19 @@
       </c>
       <c r="D43" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E43" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F43" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G43" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3346,15 +3352,15 @@
       </c>
       <c r="E59" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F59" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G59" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3590,7 +3596,7 @@
       </c>
       <c r="C68" s="7">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D68" s="7">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3598,15 +3604,15 @@
       </c>
       <c r="E68" s="7">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F68" s="8">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G68" s="8">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5078,19 +5084,19 @@
       </c>
       <c r="D121" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F121" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G121" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5110,15 +5116,15 @@
       </c>
       <c r="E122" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F122" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G122" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5214,7 +5220,7 @@
       </c>
       <c r="C126" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D126" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -5222,15 +5228,71 @@
       </c>
       <c r="E126" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F126" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G126" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>8</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="B127" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="C127" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D127" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E127" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>2</v>
+      </c>
+      <c r="F127" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>2</v>
+      </c>
+      <c r="G127" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="B128" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="C128" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D128" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E128" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>2</v>
+      </c>
+      <c r="F128" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>2</v>
+      </c>
+      <c r="G128" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5246,7 +5308,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:J999"/>
+  <dimension ref="A1:J1022"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -40220,9 +40282,814 @@
         <v>105</v>
       </c>
     </row>
+    <row r="1000" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1000" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1000" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1000" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1000" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Иван</v>
+      </c>
+      <c r="E1000" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1000" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1000" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1000" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1000" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1000" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1001" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1001" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1001" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1001" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Миша</v>
+      </c>
+      <c r="E1001" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1001" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1001" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1001" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1001" s="10">
+        <v>2</v>
+      </c>
+      <c r="J1001" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1002" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1002" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1002" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1002" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Влад</v>
+      </c>
+      <c r="E1002" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1002" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1002" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1002" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1002" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1002" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1003" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1003" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1003" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1003" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Олег Шишкин</v>
+      </c>
+      <c r="E1003" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1003" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1003" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1003" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1003" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1003" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1004" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1004" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1004" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1004" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Толя Шлаев</v>
+      </c>
+      <c r="E1004" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1004" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1004" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1004" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1004" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1004" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1005" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1005" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1005" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1005" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Женя (кипер)</v>
+      </c>
+      <c r="E1005" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1005" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1005" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1005" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="I1005" s="10">
+        <v>5</v>
+      </c>
+      <c r="J1005" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1006" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1006" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1006" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1006" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей Крюков</v>
+      </c>
+      <c r="E1006" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1006" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1006" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1006" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1006" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1006" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1007" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1007" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1007" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1007" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Коля (АК+1)</v>
+      </c>
+      <c r="E1007" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1007" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1007" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1007" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1007" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1007" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1008" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1008" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1008" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1008" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Андрей (АК+1)</v>
+      </c>
+      <c r="E1008" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1008" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1008" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1008" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1008" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1008" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1009" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1009" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1009" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1009" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Никита (АК+1)</v>
+      </c>
+      <c r="E1009" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1009" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1009" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1009" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1009" s="10">
+        <v>2</v>
+      </c>
+      <c r="J1009" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1010" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1010" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1010" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1010" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Андрей Волошин (АК+1)</v>
+      </c>
+      <c r="E1010" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1010" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1010" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1010" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1010" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1010" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1011" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1011" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1011" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1011" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Семен (АК+1)</v>
+      </c>
+      <c r="E1011" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1011" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1011" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1011" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1011" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1011" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1012" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1012" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1012" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1012" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Рамиль (АК+1)</v>
+      </c>
+      <c r="E1012" s="7">
+        <v>2</v>
+      </c>
+      <c r="F1012" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1012" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1012" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1012" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1012" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1013" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1013" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1013" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1013" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Егор (АК+1)</v>
+      </c>
+      <c r="E1013" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1013" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1013" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1013" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1013" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1013" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1014" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1014" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1014" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1014" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Саша (АК+1)</v>
+      </c>
+      <c r="E1014" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1014" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1014" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1014" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1014" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1014" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1015" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1015" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1015" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1015" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Кирилл Попов</v>
+      </c>
+      <c r="E1015" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1015" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1015" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1015" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="I1015" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1015" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1016" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1016" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1016" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1016" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Атай</v>
+      </c>
+      <c r="E1016" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1016" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1016" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1016" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="I1016" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1016" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1017" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1017" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1017" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1017" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Нурик</v>
+      </c>
+      <c r="E1017" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1017" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1017" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1017" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="I1017" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1017" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1018" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1018" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1018" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1018" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Макс Логинов</v>
+      </c>
+      <c r="E1018" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1018" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1018" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1018" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="I1018" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1018" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1019" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1019" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1019" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1019" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Эля</v>
+      </c>
+      <c r="E1019" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1019" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1019" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1019" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="I1019" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1019" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1020" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1020" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1020" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1020" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Рубик</v>
+      </c>
+      <c r="E1020" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1020" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1020" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1020" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="I1020" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1020" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1021" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1021" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1021" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1021" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Костя</v>
+      </c>
+      <c r="E1021" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1021" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1021" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1021" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="I1021" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1021" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1022" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B1022" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1022" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1022" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Паша</v>
+      </c>
+      <c r="E1022" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1022" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1022" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1022" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1022" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1022" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C914" xr:uid="{196C3799-EB98-437C-A569-9C3B494F4FE2}">
       <formula1>tel_</formula1>
     </dataValidation>
@@ -40240,7 +41107,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:E144"/>
+  <dimension ref="A1:E147"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -42697,9 +43564,60 @@
         <v>105</v>
       </c>
     </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="13">
+        <v>46128</v>
+      </c>
+      <c r="B145" s="7">
+        <v>1</v>
+      </c>
+      <c r="C145" s="8">
+        <v>2</v>
+      </c>
+      <c r="D145" s="8">
+        <v>2</v>
+      </c>
+      <c r="E145" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="13">
+        <v>46128</v>
+      </c>
+      <c r="B146" s="7">
+        <v>2</v>
+      </c>
+      <c r="C146" s="8">
+        <v>2</v>
+      </c>
+      <c r="D146" s="8">
+        <v>2</v>
+      </c>
+      <c r="E146" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="13">
+        <v>46128</v>
+      </c>
+      <c r="B147" s="7">
+        <v>3</v>
+      </c>
+      <c r="C147" s="8">
+        <v>2</v>
+      </c>
+      <c r="D147" s="8">
+        <v>4</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B144" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B147" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>

--- a/football_stats.xlsx
+++ b/football_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\football_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A52E60B-8F84-45C5-A96D-00A708F2E142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67ED7B2-05A0-498B-B983-678AFA4F8B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C8" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="G8" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C121" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D121" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="G121" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -40892,7 +40892,7 @@
         <v>Нурик</v>
       </c>
       <c r="E1017" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1017" s="8">
         <v>0</v>
@@ -40927,7 +40927,7 @@
         <v>Макс Логинов</v>
       </c>
       <c r="E1018" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1018" s="8">
         <v>1</v>

--- a/football_stats.xlsx
+++ b/football_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\football_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67ED7B2-05A0-498B-B983-678AFA4F8B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F399A21-7467-4E85-A0F4-CB5E85BF053C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2530" uniqueCount="148">
   <si>
     <t>player_id</t>
   </si>
@@ -490,6 +490,15 @@
   </si>
   <si>
     <t>Саша (АК+1)</t>
+  </si>
+  <si>
+    <t>Замрат Алимов</t>
+  </si>
+  <si>
+    <t>Мага (Руб+1)</t>
+  </si>
+  <si>
+    <t>Заур (Руб+1)</t>
   </si>
 </sst>
 </file>
@@ -1368,8 +1377,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G128" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
-  <autoFilter ref="A1:G128" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G131" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
+  <autoFilter ref="A1:G131" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G74">
     <sortCondition descending="1" ref="G1:G74"/>
   </sortState>
@@ -1397,8 +1406,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J1022" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A1:J1022" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J1050" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:J1050" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G60">
     <sortCondition ref="A1:A60"/>
   </sortState>
@@ -1425,8 +1434,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E147" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E147" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E151" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E151" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{92BE0DCE-EF0C-43B2-937D-640EBFF087A6}" name="date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{B497FB59-180E-4B72-9ECD-E25C88173489}" name="team_number" dataDxfId="3"/>
@@ -1704,7 +1713,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" style="38" bestFit="1" customWidth="1"/>
@@ -1784,15 +1793,15 @@
       </c>
       <c r="E3" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F3" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1812,15 +1821,15 @@
       </c>
       <c r="E4" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F4" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1840,15 +1849,15 @@
       </c>
       <c r="E5" s="21">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F5" s="22">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" s="22">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1868,15 +1877,15 @@
       </c>
       <c r="E6" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F6" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1888,23 +1897,23 @@
       </c>
       <c r="C7" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D7" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F7" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G7" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1916,7 +1925,7 @@
       </c>
       <c r="C8" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1924,15 +1933,15 @@
       </c>
       <c r="E8" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F8" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G8" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2084,7 +2093,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2092,15 +2101,15 @@
       </c>
       <c r="E14" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F14" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G14" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2176,15 +2185,15 @@
       </c>
       <c r="E17" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G17" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2252,7 +2261,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D20" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2260,15 +2269,15 @@
       </c>
       <c r="E20" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F20" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G20" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2280,23 +2289,23 @@
       </c>
       <c r="C21" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D21" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E21" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F21" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G21" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2312,19 +2321,19 @@
       </c>
       <c r="D22" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F22" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G22" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2400,15 +2409,15 @@
       </c>
       <c r="E25" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F25" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G25" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2484,15 +2493,15 @@
       </c>
       <c r="E28" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F28" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G28" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2536,19 +2545,19 @@
       </c>
       <c r="D30" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E30" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F30" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G30" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2588,7 +2597,7 @@
       </c>
       <c r="C32" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D32" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2596,15 +2605,15 @@
       </c>
       <c r="E32" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F32" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G32" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2680,15 +2689,15 @@
       </c>
       <c r="E35" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F35" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G35" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2756,7 +2765,7 @@
       </c>
       <c r="C38" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D38" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2764,15 +2773,15 @@
       </c>
       <c r="E38" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F38" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G38" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2848,15 +2857,15 @@
       </c>
       <c r="E41" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F41" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G41" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2868,23 +2877,23 @@
       </c>
       <c r="C42" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D42" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E42" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F42" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G42" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>56</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3484,23 +3493,23 @@
       </c>
       <c r="C64" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D64" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E64" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F64" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G64" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3904,23 +3913,23 @@
       </c>
       <c r="C79" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D79" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E79" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F79" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G79" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>135</v>
+        <v>154</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4296,23 +4305,23 @@
       </c>
       <c r="C93" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D93" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F93" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G93" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -4668,15 +4677,15 @@
       </c>
       <c r="E106" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F106" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G106" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4780,15 +4789,15 @@
       </c>
       <c r="E110" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F110" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G110" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5080,23 +5089,23 @@
       </c>
       <c r="C121" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D121" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E121" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F121" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G121" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5291,6 +5300,90 @@
         <v>2</v>
       </c>
       <c r="G128" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="B129" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="C129" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D129" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E129" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="F129" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="G129" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="B130" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="C130" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="D130" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E130" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="F130" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>2</v>
+      </c>
+      <c r="G130" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="B131" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="C131" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="D131" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E131" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="F131" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>2</v>
+      </c>
+      <c r="G131" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
         <v>4</v>
       </c>
@@ -5308,7 +5401,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:J1022"/>
+  <dimension ref="A1:J1050"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -41084,6 +41177,986 @@
         <v>0</v>
       </c>
       <c r="J1022" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1023" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1023" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1023" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D1023" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Замрат Алимов</v>
+      </c>
+      <c r="E1023" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1023" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1023" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1023" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1023" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1023" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1024" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1024" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1024" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1024" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Дима Сахаров</v>
+      </c>
+      <c r="E1024" s="7">
+        <v>3</v>
+      </c>
+      <c r="F1024" s="8">
+        <v>2</v>
+      </c>
+      <c r="G1024" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>8</v>
+      </c>
+      <c r="H1024" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1024" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1024" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1025" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1025" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1025" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1025" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Расул</v>
+      </c>
+      <c r="E1025" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1025" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1025" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1025" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1025" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1025" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1026" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1026" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1026" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1026" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Нурик</v>
+      </c>
+      <c r="E1026" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1026" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1026" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1026" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1026" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1026" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1027" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1027" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1027" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1027" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Олег Шишкин</v>
+      </c>
+      <c r="E1027" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1027" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1027" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1027" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1027" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1027" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1028" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1028" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1028" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1028" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Александр Травкин</v>
+      </c>
+      <c r="E1028" s="7">
+        <v>6</v>
+      </c>
+      <c r="F1028" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1028" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>8</v>
+      </c>
+      <c r="H1028" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1028" s="10">
+        <v>4</v>
+      </c>
+      <c r="J1028" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1029" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1029" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1029" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1029" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Кирилл Попов</v>
+      </c>
+      <c r="E1029" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1029" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1029" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1029" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1029" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1029" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1030" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1030" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1030" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1030" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Влад</v>
+      </c>
+      <c r="E1030" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1030" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1030" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1030" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1030" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1030" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1031" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1031" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1031" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1031" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Антон Копыч</v>
+      </c>
+      <c r="E1031" s="7">
+        <v>4</v>
+      </c>
+      <c r="F1031" s="8">
+        <v>5</v>
+      </c>
+      <c r="G1031" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>8</v>
+      </c>
+      <c r="H1031" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1031" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1031" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1032" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1032" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1032" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1032" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Толя Шлаев</v>
+      </c>
+      <c r="E1032" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1032" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1032" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1032" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1032" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1032" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1033" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1033" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1033" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1033" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Анашкин</v>
+      </c>
+      <c r="E1033" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1033" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1033" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1033" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1033" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1033" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1034" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1034" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1034" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1034" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Костя</v>
+      </c>
+      <c r="E1034" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1034" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1034" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1034" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1034" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1034" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1035" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1035" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1035" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1035" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей Крюков</v>
+      </c>
+      <c r="E1035" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1035" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1035" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1035" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1035" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1035" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1036" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1036" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1036" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1036" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Макс Логинов</v>
+      </c>
+      <c r="E1036" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1036" s="8">
+        <v>2</v>
+      </c>
+      <c r="G1036" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>8</v>
+      </c>
+      <c r="H1036" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1036" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1036" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1037" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1037" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1037" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1037" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Игорь Фомичев</v>
+      </c>
+      <c r="E1037" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1037" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1037" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1037" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1037" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1037" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1038" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1038" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1038" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1038" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей</v>
+      </c>
+      <c r="E1038" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1038" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1038" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1038" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1038" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1038" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1039" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1039" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1039" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1039" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Саша (Витя+1)</v>
+      </c>
+      <c r="E1039" s="7">
+        <v>2</v>
+      </c>
+      <c r="F1039" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1039" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>8</v>
+      </c>
+      <c r="H1039" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1039" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1039" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1040" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1040" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1040" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1040" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Богдан Ждамаров</v>
+      </c>
+      <c r="E1040" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1040" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1040" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1040" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1040" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1040" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1041" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1041" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1041" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1041" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Дима (Спартак)</v>
+      </c>
+      <c r="E1041" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1041" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1041" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1041" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1041" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1041" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1042" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1042" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1042" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1042" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Рубик</v>
+      </c>
+      <c r="E1042" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1042" s="8">
+        <v>2</v>
+      </c>
+      <c r="G1042" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1042" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1042" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1042" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1043" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1043" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1043" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1043" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Заур (Руб+1)</v>
+      </c>
+      <c r="E1043" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1043" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1043" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1043" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1043" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1043" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1044" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1044" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1044" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1044" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Эльдар</v>
+      </c>
+      <c r="E1044" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1044" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1044" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1044" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1044" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1044" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1045" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1045" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1045" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1045" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Рома Сурнин</v>
+      </c>
+      <c r="E1045" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1045" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1045" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1045" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1045" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1045" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1046" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1046" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1046" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1046" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Атай</v>
+      </c>
+      <c r="E1046" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1046" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1046" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>8</v>
+      </c>
+      <c r="H1046" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1046" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1046" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1047" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1047" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1047" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1047" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Никита</v>
+      </c>
+      <c r="E1047" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1047" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1047" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1047" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1047" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1047" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1048" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1048" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1048" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1048" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Артем Ширяев</v>
+      </c>
+      <c r="E1048" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1048" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1048" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1048" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1048" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1048" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1049" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1049" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1049" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1049" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Женя Одушкин</v>
+      </c>
+      <c r="E1049" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1049" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1049" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>8</v>
+      </c>
+      <c r="H1049" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1049" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1049" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1050" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B1050" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1050" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1050" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Мага (Руб+1)</v>
+      </c>
+      <c r="E1050" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1050" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1050" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1050" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1050" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1050" s="16" t="s">
         <v>105</v>
       </c>
     </row>
@@ -41107,7 +42180,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:E147"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -43615,9 +44688,77 @@
         <v>105</v>
       </c>
     </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="13">
+        <v>46131</v>
+      </c>
+      <c r="B148" s="7">
+        <v>1</v>
+      </c>
+      <c r="C148" s="8">
+        <v>8</v>
+      </c>
+      <c r="D148" s="8">
+        <v>2</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="13">
+        <v>46131</v>
+      </c>
+      <c r="B149" s="7">
+        <v>2</v>
+      </c>
+      <c r="C149" s="8">
+        <v>1</v>
+      </c>
+      <c r="D149" s="8">
+        <v>1</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="13">
+        <v>46131</v>
+      </c>
+      <c r="B150" s="7">
+        <v>3</v>
+      </c>
+      <c r="C150" s="8">
+        <v>1</v>
+      </c>
+      <c r="D150" s="8">
+        <v>1</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="13">
+        <v>46131</v>
+      </c>
+      <c r="B151" s="7">
+        <v>4</v>
+      </c>
+      <c r="C151" s="8">
+        <v>1</v>
+      </c>
+      <c r="D151" s="8">
+        <v>2</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B147" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B151" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>

--- a/football_stats.xlsx
+++ b/football_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\football_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E635169F-4CDD-4572-AA0A-BF0405B606E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC45A1E-2F03-4F6A-875B-5E9AE5390F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2530" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2600" uniqueCount="151">
   <si>
     <t>player_id</t>
   </si>
@@ -499,6 +499,15 @@
   </si>
   <si>
     <t>Антон Копач</t>
+  </si>
+  <si>
+    <t>Ях Я</t>
+  </si>
+  <si>
+    <t>Андрей (Руб+1)</t>
+  </si>
+  <si>
+    <t>Мухамед (Руб+1)</t>
   </si>
 </sst>
 </file>
@@ -1377,8 +1386,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G131" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
-  <autoFilter ref="A1:G131" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G134" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
+  <autoFilter ref="A1:G134" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G74">
     <sortCondition descending="1" ref="G1:G74"/>
   </sortState>
@@ -1406,8 +1415,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J1050" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A1:J1050" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J1080" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:J1080" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G60">
     <sortCondition ref="A1:A60"/>
   </sortState>
@@ -1434,8 +1443,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E151" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E151" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E155" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E155" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{92BE0DCE-EF0C-43B2-937D-640EBFF087A6}" name="date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{B497FB59-180E-4B72-9ECD-E25C88173489}" name="team_number" dataDxfId="3"/>
@@ -1713,7 +1722,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" style="38" bestFit="1" customWidth="1"/>
@@ -1793,15 +1802,15 @@
       </c>
       <c r="E3" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F3" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1813,7 +1822,7 @@
       </c>
       <c r="C4" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1821,15 +1830,15 @@
       </c>
       <c r="E4" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F4" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1873,19 +1882,19 @@
       </c>
       <c r="D6" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F6" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1925,23 +1934,23 @@
       </c>
       <c r="C8" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D8" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E8" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="F8" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>200</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2037,23 +2046,23 @@
       </c>
       <c r="C12" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D12" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E12" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="F12" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G12" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>234</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2105,11 +2114,11 @@
       </c>
       <c r="F14" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G14" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2177,23 +2186,23 @@
       </c>
       <c r="C17" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D17" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E17" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F17" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2265,19 +2274,19 @@
       </c>
       <c r="D20" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E20" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F20" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G20" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2289,23 +2298,23 @@
       </c>
       <c r="C21" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D21" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E21" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="F21" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G21" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>189</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2401,23 +2410,23 @@
       </c>
       <c r="C25" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D25" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E25" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F25" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G25" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2549,15 +2558,15 @@
       </c>
       <c r="E30" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F30" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G30" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2601,7 +2610,7 @@
       </c>
       <c r="D32" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E32" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2609,11 +2618,11 @@
       </c>
       <c r="F32" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G32" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2681,23 +2690,23 @@
       </c>
       <c r="C35" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D35" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E35" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F35" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G35" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2745,15 +2754,15 @@
       </c>
       <c r="E37" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F37" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G37" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2805,11 +2814,11 @@
       </c>
       <c r="F39" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G39" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2861,11 +2870,11 @@
       </c>
       <c r="F41" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G41" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2905,7 +2914,7 @@
       </c>
       <c r="C43" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D43" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2917,11 +2926,11 @@
       </c>
       <c r="F43" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G43" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3493,7 +3502,7 @@
       </c>
       <c r="C64" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D64" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3501,15 +3510,15 @@
       </c>
       <c r="E64" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F64" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G64" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3617,11 +3626,11 @@
       </c>
       <c r="F68" s="8">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G68" s="8">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3921,15 +3930,15 @@
       </c>
       <c r="E79" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F79" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G79" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4169,19 +4178,19 @@
       </c>
       <c r="D88" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E88" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F88" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4669,7 +4678,7 @@
       </c>
       <c r="C106" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D106" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -4681,11 +4690,11 @@
       </c>
       <c r="F106" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G106" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4789,15 +4798,15 @@
       </c>
       <c r="E110" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F110" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G110" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5065,19 +5074,19 @@
       </c>
       <c r="D120" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E120" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F120" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G120" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5089,7 +5098,7 @@
       </c>
       <c r="C121" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D121" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -5097,15 +5106,15 @@
       </c>
       <c r="E121" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F121" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G121" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5209,15 +5218,15 @@
       </c>
       <c r="E125" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F125" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G125" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5349,15 +5358,15 @@
       </c>
       <c r="E130" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F130" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G130" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -5386,6 +5395,90 @@
       <c r="G131" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
         <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="B132" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="C132" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D132" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E132" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>5</v>
+      </c>
+      <c r="F132" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="G132" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="B133" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="C133" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>6</v>
+      </c>
+      <c r="D133" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E133" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>5</v>
+      </c>
+      <c r="F133" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="G133" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="B134" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="C134" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D134" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E134" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="F134" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="G134" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5401,7 +5494,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:J1050"/>
+  <dimension ref="A1:J1080"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -42157,6 +42250,1056 @@
         <v>0</v>
       </c>
       <c r="J1050" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1051" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1051" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1051" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1051" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Кирилл Попов</v>
+      </c>
+      <c r="E1051" s="7">
+        <v>2</v>
+      </c>
+      <c r="F1051" s="8">
+        <v>3</v>
+      </c>
+      <c r="G1051" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>9</v>
+      </c>
+      <c r="H1051" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1051" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1051" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1052" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1052" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1052" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1052" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Арги</v>
+      </c>
+      <c r="E1052" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1052" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1052" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1052" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1052" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1052" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1053" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1053" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1053" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1053" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Антон Копач</v>
+      </c>
+      <c r="E1053" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1053" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1053" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1053" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1053" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1053" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1054" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1054" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1054" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1054" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Нурик</v>
+      </c>
+      <c r="E1054" s="7">
+        <v>3</v>
+      </c>
+      <c r="F1054" s="8">
+        <v>2</v>
+      </c>
+      <c r="G1054" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>9</v>
+      </c>
+      <c r="H1054" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1054" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1054" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1055" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1055" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1055" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1055" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Костя</v>
+      </c>
+      <c r="E1055" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1055" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1055" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1055" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1055" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1055" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1056" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1056" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1056" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1056" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Анашкин</v>
+      </c>
+      <c r="E1056" s="7">
+        <v>2</v>
+      </c>
+      <c r="F1056" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1056" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1056" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1056" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1056" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1057" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1057" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1057" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1057" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Расул</v>
+      </c>
+      <c r="E1057" s="7">
+        <v>2</v>
+      </c>
+      <c r="F1057" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1057" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H1057" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1057" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1057" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1058" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1058" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1058" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1058" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей Крюков</v>
+      </c>
+      <c r="E1058" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1058" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1058" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1058" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1058" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1058" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1059" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1059" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1059" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1059" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Женя (кипер)</v>
+      </c>
+      <c r="E1059" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1059" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1059" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="H1059" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1059" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1059" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1060" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1060" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1060" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1060" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Олег Шишкин</v>
+      </c>
+      <c r="E1060" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1060" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1060" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="H1060" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1060" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1060" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1061" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1061" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1061" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1061" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Игорь Фомичев</v>
+      </c>
+      <c r="E1061" s="7">
+        <v>2</v>
+      </c>
+      <c r="F1061" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1061" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>9</v>
+      </c>
+      <c r="H1061" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1061" s="10">
+        <v>4</v>
+      </c>
+      <c r="J1061" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1062" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1062" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1062" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1062" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Андрей (АК+1)</v>
+      </c>
+      <c r="E1062" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1062" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1062" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="H1062" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1062" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1062" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1063" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1063" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1063" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1063" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Дядя Руслан</v>
+      </c>
+      <c r="E1063" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1063" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1063" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>9</v>
+      </c>
+      <c r="H1063" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1063" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1063" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1064" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1064" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1064" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1064" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Хамзат (Расул+1)</v>
+      </c>
+      <c r="E1064" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1064" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1064" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H1064" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1064" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1064" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1065" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1065" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1065" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1065" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Ях Я</v>
+      </c>
+      <c r="E1065" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1065" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1065" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H1065" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1065" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1065" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1066" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1066" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1066" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D1066" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Мага (Руб+1)</v>
+      </c>
+      <c r="E1066" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1066" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1066" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H1066" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1066" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1066" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1067" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1067" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1067" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1067" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Богдан Ждамаров</v>
+      </c>
+      <c r="E1067" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1067" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1067" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>9</v>
+      </c>
+      <c r="H1067" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1067" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1067" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1068" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1068" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1068" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1068" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Эльдар</v>
+      </c>
+      <c r="E1068" s="7">
+        <v>2</v>
+      </c>
+      <c r="F1068" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1068" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1068" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1068" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1068" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1069" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1069" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1069" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1069" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей</v>
+      </c>
+      <c r="E1069" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1069" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1069" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1069" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1069" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1069" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1070" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1070" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1070" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1070" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Андрей (Руб+1)</v>
+      </c>
+      <c r="E1070" s="7">
+        <v>6</v>
+      </c>
+      <c r="F1070" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1070" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H1070" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1070" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1070" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1071" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1071" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1071" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1071" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Рубик</v>
+      </c>
+      <c r="E1071" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1071" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1071" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H1071" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1071" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1071" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1072" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1072" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1072" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1072" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Руслан Байшев</v>
+      </c>
+      <c r="E1072" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1072" s="8">
+        <v>3</v>
+      </c>
+      <c r="G1072" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H1072" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1072" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1072" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1073" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1073" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1073" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1073" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Юра Пименов</v>
+      </c>
+      <c r="E1073" s="7">
+        <v>4</v>
+      </c>
+      <c r="F1073" s="8">
+        <v>6</v>
+      </c>
+      <c r="G1073" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>9</v>
+      </c>
+      <c r="H1073" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1073" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1073" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1074" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1074" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1074" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1074" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Рома Сурнин</v>
+      </c>
+      <c r="E1074" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1074" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1074" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="H1074" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1074" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1074" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1075" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1075" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1075" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1075" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Егор (АК+1)</v>
+      </c>
+      <c r="E1075" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1075" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1075" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="H1075" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1075" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1075" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1076" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1076" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1076" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1076" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Атай</v>
+      </c>
+      <c r="E1076" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1076" s="8">
+        <v>2</v>
+      </c>
+      <c r="G1076" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H1076" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1076" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1076" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1077" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1077" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1077" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1077" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Макс Логинов</v>
+      </c>
+      <c r="E1077" s="7">
+        <v>4</v>
+      </c>
+      <c r="F1077" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1077" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>9</v>
+      </c>
+      <c r="H1077" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1077" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1077" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1078" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1078" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1078" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1078" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Женя Одушкин</v>
+      </c>
+      <c r="E1078" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1078" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1078" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="H1078" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1078" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1078" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1079" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1079" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1079" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1079" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Дима (Спартак)</v>
+      </c>
+      <c r="E1079" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1079" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1079" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="H1079" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1079" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1079" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1080" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B1080" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1080" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1080" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Мухамед (Руб+1)</v>
+      </c>
+      <c r="E1080" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1080" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1080" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="H1080" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1080" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1080" s="16" t="s">
         <v>104</v>
       </c>
     </row>
@@ -42180,7 +43323,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:E151"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -44756,9 +45899,77 @@
         <v>104</v>
       </c>
     </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="13">
+        <v>46138</v>
+      </c>
+      <c r="B152" s="7">
+        <v>1</v>
+      </c>
+      <c r="C152" s="8">
+        <v>2</v>
+      </c>
+      <c r="D152" s="8">
+        <v>1</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="13">
+        <v>46138</v>
+      </c>
+      <c r="B153" s="7">
+        <v>2</v>
+      </c>
+      <c r="C153" s="8">
+        <v>9</v>
+      </c>
+      <c r="D153" s="8">
+        <v>1</v>
+      </c>
+      <c r="E153" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="13">
+        <v>46138</v>
+      </c>
+      <c r="B154" s="7">
+        <v>3</v>
+      </c>
+      <c r="C154" s="8">
+        <v>0</v>
+      </c>
+      <c r="D154" s="8">
+        <v>1</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="13">
+        <v>46138</v>
+      </c>
+      <c r="B155" s="7">
+        <v>4</v>
+      </c>
+      <c r="C155" s="8">
+        <v>5</v>
+      </c>
+      <c r="D155" s="8">
+        <v>1</v>
+      </c>
+      <c r="E155" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B151" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B155" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>

--- a/football_stats.xlsx
+++ b/football_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\football_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC45A1E-2F03-4F6A-875B-5E9AE5390F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CDE161-5624-476A-A977-A4AFF6FACDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2600" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2647" uniqueCount="152">
   <si>
     <t>player_id</t>
   </si>
@@ -508,6 +508,9 @@
   </si>
   <si>
     <t>Мухамед (Руб+1)</t>
+  </si>
+  <si>
+    <t>Костя +1</t>
   </si>
 </sst>
 </file>
@@ -1386,8 +1389,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G134" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
-  <autoFilter ref="A1:G134" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G135" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
+  <autoFilter ref="A1:G135" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G74">
     <sortCondition descending="1" ref="G1:G74"/>
   </sortState>
@@ -1415,8 +1418,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J1080" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A1:J1080" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J1101" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:J1101" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G60">
     <sortCondition ref="A1:A60"/>
   </sortState>
@@ -1443,8 +1446,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E155" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E155" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E158" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E158" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{92BE0DCE-EF0C-43B2-937D-640EBFF087A6}" name="date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{B497FB59-180E-4B72-9ECD-E25C88173489}" name="team_number" dataDxfId="3"/>
@@ -1722,7 +1725,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" style="38" bestFit="1" customWidth="1"/>
@@ -1766,15 +1769,15 @@
       </c>
       <c r="C2" s="19">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D2" s="19">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" s="19">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F2" s="20">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1782,7 +1785,7 @@
       </c>
       <c r="G2" s="20">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>198</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1806,11 +1809,11 @@
       </c>
       <c r="F3" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1854,19 +1857,19 @@
       </c>
       <c r="D5" s="21">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="21">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F5" s="22">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" s="22">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1878,7 +1881,7 @@
       </c>
       <c r="C6" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D6" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1886,15 +1889,15 @@
       </c>
       <c r="E6" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="F6" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>234</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1934,7 +1937,7 @@
       </c>
       <c r="C8" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D8" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1942,15 +1945,15 @@
       </c>
       <c r="E8" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F8" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>215</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2046,15 +2049,15 @@
       </c>
       <c r="C12" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D12" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E12" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F12" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2062,7 +2065,7 @@
       </c>
       <c r="G12" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2130,7 +2133,7 @@
       </c>
       <c r="C15" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2142,11 +2145,11 @@
       </c>
       <c r="F15" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2214,23 +2217,23 @@
       </c>
       <c r="C18" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E18" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F18" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2254,11 +2257,11 @@
       </c>
       <c r="F19" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2334,7 +2337,7 @@
       </c>
       <c r="E22" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F22" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2342,7 +2345,7 @@
       </c>
       <c r="G22" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2358,7 +2361,7 @@
       </c>
       <c r="D23" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E23" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2366,11 +2369,11 @@
       </c>
       <c r="F23" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G23" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2414,11 +2417,11 @@
       </c>
       <c r="D25" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E25" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F25" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2426,7 +2429,7 @@
       </c>
       <c r="G25" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2590,11 +2593,11 @@
       </c>
       <c r="F31" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2810,7 +2813,7 @@
       </c>
       <c r="E39" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F39" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2818,7 +2821,7 @@
       </c>
       <c r="G39" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3062,15 +3065,15 @@
       </c>
       <c r="E48" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F48" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G48" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3510,7 +3513,7 @@
       </c>
       <c r="E64" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F64" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3518,7 +3521,7 @@
       </c>
       <c r="G64" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -4062,23 +4065,23 @@
       </c>
       <c r="C84" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E84" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F84" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4146,23 +4149,23 @@
       </c>
       <c r="C87" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D87" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E87" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F87" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G87" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4802,11 +4805,11 @@
       </c>
       <c r="F110" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G110" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5098,15 +5101,15 @@
       </c>
       <c r="C121" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D121" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E121" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F121" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -5114,7 +5117,7 @@
       </c>
       <c r="G121" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5477,6 +5480,34 @@
         <v>1</v>
       </c>
       <c r="G134" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="B135" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="C135" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D135" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E135" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="F135" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="G135" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
         <v>1</v>
       </c>
@@ -5494,7 +5525,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:J1080"/>
+  <dimension ref="A1:J1101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -43300,6 +43331,741 @@
         <v>0</v>
       </c>
       <c r="J1080" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1081" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1081" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1081" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1081" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Влад</v>
+      </c>
+      <c r="E1081" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1081" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1081" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1081" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1081" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1081" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1082" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1082" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1082" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1082" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Энтони Тепеев</v>
+      </c>
+      <c r="E1082" s="7">
+        <v>4</v>
+      </c>
+      <c r="F1082" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1082" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1082" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1082" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1082" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1083" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1083" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1083" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1083" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Паша</v>
+      </c>
+      <c r="E1083" s="7">
+        <v>5</v>
+      </c>
+      <c r="F1083" s="8">
+        <v>2</v>
+      </c>
+      <c r="G1083" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1083" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1083" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1083" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1084" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1084" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1084" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1084" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Толя Шлаев</v>
+      </c>
+      <c r="E1084" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1084" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1084" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1084" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1084" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1084" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1085" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1085" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1085" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1085" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Костя</v>
+      </c>
+      <c r="E1085" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1085" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1085" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="H1085" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1085" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1085" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1086" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1086" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1086" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1086" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Александр Костюнин</v>
+      </c>
+      <c r="E1086" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1086" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1086" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="H1086" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1086" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1086" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1087" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1087" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1087" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1087" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Юра Пименов</v>
+      </c>
+      <c r="E1087" s="7">
+        <v>4</v>
+      </c>
+      <c r="F1087" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1087" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1087" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1087" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1087" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1088" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1088" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1088" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1088" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Макс Логинов</v>
+      </c>
+      <c r="E1088" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1088" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1088" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1088" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1088" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1088" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1089" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1089" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1089" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1089" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Нурик</v>
+      </c>
+      <c r="E1089" s="7">
+        <v>5</v>
+      </c>
+      <c r="F1089" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1089" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1089" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1089" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1089" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1090" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1090" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1090" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1090" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Кирилл Попов</v>
+      </c>
+      <c r="E1090" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1090" s="8">
+        <v>2</v>
+      </c>
+      <c r="G1090" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1090" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1090" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1090" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1091" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1091" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1091" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1091" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Витя</v>
+      </c>
+      <c r="E1091" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1091" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1091" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="H1091" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1091" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1091" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1092" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1092" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1092" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1092" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Женя (кипер)</v>
+      </c>
+      <c r="E1092" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1092" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1092" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1092" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1092" s="10">
+        <v>4</v>
+      </c>
+      <c r="J1092" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1093" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1093" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1093" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1093" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Жора</v>
+      </c>
+      <c r="E1093" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1093" s="8">
+        <v>3</v>
+      </c>
+      <c r="G1093" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1093" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1093" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1093" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1094" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1094" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1094" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1094" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Вова</v>
+      </c>
+      <c r="E1094" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1094" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1094" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1094" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1094" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1094" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1095" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1095" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1095" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1095" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Анашкин</v>
+      </c>
+      <c r="E1095" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1095" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1095" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1095" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1095" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1095" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1096" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1096" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1096" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1096" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей Крюков</v>
+      </c>
+      <c r="E1096" s="7">
+        <v>2</v>
+      </c>
+      <c r="F1096" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1096" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1096" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1096" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1096" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1097" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1097" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1097" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1097" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Иван</v>
+      </c>
+      <c r="E1097" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1097" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1097" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="H1097" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1097" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1097" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1098" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1098" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1098" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1098" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Костя +1</v>
+      </c>
+      <c r="E1098" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1098" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1098" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="H1098" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1098" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1098" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1099" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1099" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1099" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1099" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Назар (Женя +1)</v>
+      </c>
+      <c r="E1099" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1099" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1099" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="H1099" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1099" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1099" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1100" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1100" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1100" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1100" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Даня (сын Вити)</v>
+      </c>
+      <c r="E1100" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1100" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1100" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1100" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1100" s="10">
+        <v>2</v>
+      </c>
+      <c r="J1100" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1101" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B1101" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1101" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1101" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Богдан Ждамаров</v>
+      </c>
+      <c r="E1101" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1101" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1101" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="H1101" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1101" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1101" s="16" t="s">
         <v>104</v>
       </c>
     </row>
@@ -43323,7 +44089,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:E155"/>
+  <dimension ref="A1:E158"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -45967,9 +46733,60 @@
         <v>104</v>
       </c>
     </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="13">
+        <v>46142</v>
+      </c>
+      <c r="B156" s="7">
+        <v>1</v>
+      </c>
+      <c r="C156" s="8">
+        <v>6</v>
+      </c>
+      <c r="D156" s="8">
+        <v>0</v>
+      </c>
+      <c r="E156" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="13">
+        <v>46142</v>
+      </c>
+      <c r="B157" s="7">
+        <v>2</v>
+      </c>
+      <c r="C157" s="8">
+        <v>6</v>
+      </c>
+      <c r="D157" s="8">
+        <v>1</v>
+      </c>
+      <c r="E157" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="13">
+        <v>46142</v>
+      </c>
+      <c r="B158" s="7">
+        <v>3</v>
+      </c>
+      <c r="C158" s="8">
+        <v>0</v>
+      </c>
+      <c r="D158" s="8">
+        <v>1</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B155" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B158" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>

--- a/football_stats.xlsx
+++ b/football_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\football_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CDE161-5624-476A-A977-A4AFF6FACDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1412B8A-BA0E-46D5-BA7F-EA2ED4CF0B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2647" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2735" uniqueCount="155">
   <si>
     <t>player_id</t>
   </si>
@@ -511,6 +511,15 @@
   </si>
   <si>
     <t>Костя +1</t>
+  </si>
+  <si>
+    <t>Алексей (0305)</t>
+  </si>
+  <si>
+    <t>Сурэн</t>
+  </si>
+  <si>
+    <t>Артур (АК+1)</t>
   </si>
 </sst>
 </file>
@@ -1389,8 +1398,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G135" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
-  <autoFilter ref="A1:G135" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G138" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
+  <autoFilter ref="A1:G138" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G74">
     <sortCondition descending="1" ref="G1:G74"/>
   </sortState>
@@ -1418,8 +1427,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J1101" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A1:J1101" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J1140" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:J1140" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G60">
     <sortCondition ref="A1:A60"/>
   </sortState>
@@ -1446,8 +1455,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E158" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E158" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E162" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E162" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{92BE0DCE-EF0C-43B2-937D-640EBFF087A6}" name="date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{B497FB59-180E-4B72-9ECD-E25C88173489}" name="team_number" dataDxfId="3"/>
@@ -1725,7 +1734,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" style="38" bestFit="1" customWidth="1"/>
@@ -1769,23 +1778,23 @@
       </c>
       <c r="C2" s="19">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D2" s="19">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="19">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F2" s="20">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="20">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1805,15 +1814,15 @@
       </c>
       <c r="E3" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F3" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1833,15 +1842,15 @@
       </c>
       <c r="E4" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F4" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1889,15 +1898,15 @@
       </c>
       <c r="E6" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F6" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1941,11 +1950,11 @@
       </c>
       <c r="D8" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F8" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1953,7 +1962,7 @@
       </c>
       <c r="G8" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2049,23 +2058,23 @@
       </c>
       <c r="C12" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D12" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E12" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F12" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G12" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>265</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2161,23 +2170,23 @@
       </c>
       <c r="C16" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E16" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F16" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2197,7 +2206,7 @@
       </c>
       <c r="E17" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F17" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2205,7 +2214,7 @@
       </c>
       <c r="G17" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2217,23 +2226,23 @@
       </c>
       <c r="C18" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E18" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F18" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G18" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>153</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2281,7 +2290,7 @@
       </c>
       <c r="E20" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F20" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2289,7 +2298,7 @@
       </c>
       <c r="G20" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2301,23 +2310,23 @@
       </c>
       <c r="C21" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D21" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E21" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F21" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G21" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>202</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2357,23 +2366,23 @@
       </c>
       <c r="C23" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D23" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E23" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F23" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G23" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>187</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2617,15 +2626,15 @@
       </c>
       <c r="E32" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F32" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G32" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2693,7 +2702,7 @@
       </c>
       <c r="C35" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D35" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2701,15 +2710,15 @@
       </c>
       <c r="E35" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F35" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G35" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2785,7 +2794,7 @@
       </c>
       <c r="E38" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F38" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2793,7 +2802,7 @@
       </c>
       <c r="G38" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2813,15 +2822,15 @@
       </c>
       <c r="E39" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="F39" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G39" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2893,19 +2902,19 @@
       </c>
       <c r="D42" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E42" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F42" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G42" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2925,7 +2934,7 @@
       </c>
       <c r="E43" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F43" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2933,7 +2942,7 @@
       </c>
       <c r="G43" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3065,7 +3074,7 @@
       </c>
       <c r="E48" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F48" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3073,7 +3082,7 @@
       </c>
       <c r="G48" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3141,15 +3150,15 @@
       </c>
       <c r="C51" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F51" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3157,7 +3166,7 @@
       </c>
       <c r="G51" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3253,7 +3262,7 @@
       </c>
       <c r="C55" s="7">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55" s="7">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3261,7 +3270,7 @@
       </c>
       <c r="E55" s="7">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F55" s="8">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3269,7 +3278,7 @@
       </c>
       <c r="G55" s="8">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3365,7 +3374,7 @@
       </c>
       <c r="C59" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D59" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3373,7 +3382,7 @@
       </c>
       <c r="E59" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F59" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3381,7 +3390,7 @@
       </c>
       <c r="G59" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3513,15 +3522,15 @@
       </c>
       <c r="E64" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F64" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G64" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3645,7 +3654,7 @@
       </c>
       <c r="C69" s="7">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" s="7">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3653,7 +3662,7 @@
       </c>
       <c r="E69" s="7">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F69" s="8">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3661,7 +3670,7 @@
       </c>
       <c r="G69" s="8">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3841,7 +3850,7 @@
       </c>
       <c r="C76" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D76" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3849,7 +3858,7 @@
       </c>
       <c r="E76" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F76" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3857,7 +3866,7 @@
       </c>
       <c r="G76" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -4401,7 +4410,7 @@
       </c>
       <c r="C96" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D96" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -4409,7 +4418,7 @@
       </c>
       <c r="E96" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F96" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -4417,7 +4426,7 @@
       </c>
       <c r="G96" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4801,7 +4810,7 @@
       </c>
       <c r="E110" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F110" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -4809,7 +4818,7 @@
       </c>
       <c r="G110" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5073,23 +5082,23 @@
       </c>
       <c r="C120" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D120" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E120" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F120" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G120" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5105,19 +5114,19 @@
       </c>
       <c r="D121" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E121" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F121" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G121" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5193,15 +5202,15 @@
       </c>
       <c r="E124" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F124" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G124" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -5213,7 +5222,7 @@
       </c>
       <c r="C125" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D125" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -5221,7 +5230,7 @@
       </c>
       <c r="E125" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F125" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -5229,7 +5238,7 @@
       </c>
       <c r="G125" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -5245,11 +5254,11 @@
       </c>
       <c r="D126" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E126" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F126" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -5257,7 +5266,7 @@
       </c>
       <c r="G126" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5437,7 +5446,7 @@
       </c>
       <c r="C133" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D133" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -5445,7 +5454,7 @@
       </c>
       <c r="E133" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F133" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -5453,7 +5462,7 @@
       </c>
       <c r="G133" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -5473,15 +5482,15 @@
       </c>
       <c r="E134" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F134" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G134" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5510,6 +5519,90 @@
       <c r="G135" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
         <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="B136" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="C136" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D136" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E136" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>7</v>
+      </c>
+      <c r="F136" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="G136" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="B137" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="C137" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="D137" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="E137" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>7</v>
+      </c>
+      <c r="F137" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="G137" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="B138" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="C138" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D138" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="E138" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="F138" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="G138" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5525,7 +5618,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:J1101"/>
+  <dimension ref="A1:J1140"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -44069,9 +44162,1374 @@
         <v>104</v>
       </c>
     </row>
+    <row r="1102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1102" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1102" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1102" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1102" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Максим Строцкий</v>
+      </c>
+      <c r="E1102" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1102" s="8">
+        <v>2</v>
+      </c>
+      <c r="G1102" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>7</v>
+      </c>
+      <c r="H1102" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1102" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1102" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1103" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1103" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1103" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1103" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Богдан Ждамаров</v>
+      </c>
+      <c r="E1103" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1103" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1103" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1103" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1103" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1103" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1104" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1104" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1104" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1104" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Фуад</v>
+      </c>
+      <c r="E1104" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1104" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1104" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1104" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1104" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1104" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1105" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1105" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1105" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1105" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Дима Сахаров</v>
+      </c>
+      <c r="E1105" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1105" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1105" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>7</v>
+      </c>
+      <c r="H1105" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1105" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1105" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1106" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1106" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1106" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1106" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Алексей (0305)</v>
+      </c>
+      <c r="E1106" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1106" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1106" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>7</v>
+      </c>
+      <c r="H1106" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1106" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1106" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1107" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1107" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1107" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1107" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Витя</v>
+      </c>
+      <c r="E1107" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1107" s="8">
+        <v>3</v>
+      </c>
+      <c r="G1107" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1107" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1107" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1107" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1108" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1108" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1108" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1108" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Юра Пименов</v>
+      </c>
+      <c r="E1108" s="7">
+        <v>6</v>
+      </c>
+      <c r="F1108" s="8">
+        <v>3</v>
+      </c>
+      <c r="G1108" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>7</v>
+      </c>
+      <c r="H1108" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1108" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1108" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1109" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1109" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1109" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1109" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Вова</v>
+      </c>
+      <c r="E1109" s="7">
+        <v>2</v>
+      </c>
+      <c r="F1109" s="8">
+        <v>2</v>
+      </c>
+      <c r="G1109" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>7</v>
+      </c>
+      <c r="H1109" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1109" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1109" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1110" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1110" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1110" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1110" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Никита (АК+1)</v>
+      </c>
+      <c r="E1110" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1110" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1110" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1110" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1110" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1110" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1111" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1111" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1111" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1111" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Паша</v>
+      </c>
+      <c r="E1111" s="7">
+        <v>3</v>
+      </c>
+      <c r="F1111" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1111" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1111" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1111" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1111" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1112" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1112" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1112" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1112" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Арги</v>
+      </c>
+      <c r="E1112" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1112" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1112" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1112" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1112" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1112" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1113" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1113" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1113" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1113" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Зинаддин Алимов</v>
+      </c>
+      <c r="E1113" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1113" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1113" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1113" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1113" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1113" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1114" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1114" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1114" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1114" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей</v>
+      </c>
+      <c r="E1114" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1114" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1114" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1114" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1114" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1114" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1115" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1115" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1115" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1115" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Женя (кипер)</v>
+      </c>
+      <c r="E1115" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1115" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1115" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>7</v>
+      </c>
+      <c r="H1115" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1115" s="10">
+        <v>5</v>
+      </c>
+      <c r="J1115" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1116" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1116" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1116" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1116" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Макс Логинов</v>
+      </c>
+      <c r="E1116" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1116" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1116" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1116" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1116" s="10">
+        <v>4</v>
+      </c>
+      <c r="J1116" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1117" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1117" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1117" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1117" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Анашкин</v>
+      </c>
+      <c r="E1117" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1117" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1117" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1117" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1117" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1117" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1118" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1118" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1118" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1118" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Костя</v>
+      </c>
+      <c r="E1118" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1118" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1118" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1118" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1118" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1118" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1119" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1119" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1119" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1119" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Коля (АК+1)</v>
+      </c>
+      <c r="E1119" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1119" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1119" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1119" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1119" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1119" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1120" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1120" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1120" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1120" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Никита</v>
+      </c>
+      <c r="E1120" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1120" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1120" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1120" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1120" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1120" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1121" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1121" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1121" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1121" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Игорь Фомичев</v>
+      </c>
+      <c r="E1121" s="7">
+        <v>2</v>
+      </c>
+      <c r="F1121" s="8">
+        <v>3</v>
+      </c>
+      <c r="G1121" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>7</v>
+      </c>
+      <c r="H1121" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1121" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1121" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1122" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1122" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1122" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1122" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей Крюков</v>
+      </c>
+      <c r="E1122" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1122" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1122" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1122" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1122" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1122" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1123" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1123" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1123" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1123" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сурэн</v>
+      </c>
+      <c r="E1123" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1123" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1123" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>7</v>
+      </c>
+      <c r="H1123" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1123" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1123" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1124" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1124" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1124" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1124" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Женя Одушкин</v>
+      </c>
+      <c r="E1124" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1124" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1124" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1124" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1124" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1124" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1125" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1125" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1125" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1125" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Энрике (Энтони+1)</v>
+      </c>
+      <c r="E1125" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1125" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1125" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>7</v>
+      </c>
+      <c r="H1125" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1125" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1125" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1126" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1126" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1126" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1126" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Даня (сын Вити)</v>
+      </c>
+      <c r="E1126" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1126" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1126" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1126" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1126" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1126" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1127" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1127" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1127" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1127" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Нурик</v>
+      </c>
+      <c r="E1127" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1127" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1127" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1127" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1127" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1127" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1128" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1128" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1128" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1128" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Фуад</v>
+      </c>
+      <c r="E1128" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1128" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1128" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1128" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1128" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1128" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1129" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1129" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1129" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1129" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Андрей (АК+1)</v>
+      </c>
+      <c r="E1129" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1129" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1129" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1129" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1129" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1129" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1130" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1130" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1130" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1130" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Илья (АК+1)</v>
+      </c>
+      <c r="E1130" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1130" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1130" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1130" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1130" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1130" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1131" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1131" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1131" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1131" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Коля (АК+1)</v>
+      </c>
+      <c r="E1131" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1131" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1131" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1131" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1131" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1131" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1132" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1132" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1132" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1132" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Эльдар</v>
+      </c>
+      <c r="E1132" s="7">
+        <v>2</v>
+      </c>
+      <c r="F1132" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1132" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1132" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1132" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1132" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1133" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1133" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1133" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1133" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Дима (Руб)</v>
+      </c>
+      <c r="E1133" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1133" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1133" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1133" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1133" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1133" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1134" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1134" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1134" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1134" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Расул</v>
+      </c>
+      <c r="E1134" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1134" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1134" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1134" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1134" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1134" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1135" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1135" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1135" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1135" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Мухамед (Руб+1)</v>
+      </c>
+      <c r="E1135" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1135" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1135" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>7</v>
+      </c>
+      <c r="H1135" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1135" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1135" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1136" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1136" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1136" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1136" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Андрей (Руб+1)</v>
+      </c>
+      <c r="E1136" s="7">
+        <v>2</v>
+      </c>
+      <c r="F1136" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1136" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1136" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1136" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1136" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1137" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1137" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1137" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1137" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Артур (АК+1)</v>
+      </c>
+      <c r="E1137" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1137" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1137" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1137" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1137" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1137" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1138" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1138" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1138" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1138" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Атай</v>
+      </c>
+      <c r="E1138" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1138" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1138" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1138" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1138" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1138" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1139" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1139" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1139" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1139" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Игорь (Ник +1)</v>
+      </c>
+      <c r="E1139" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1139" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1139" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1139" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1139" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1139" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1140" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B1140" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1140" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1140" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Хамзат (Расул+1)</v>
+      </c>
+      <c r="E1140" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1140" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1140" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1140" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1140" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1140" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C914" xr:uid="{196C3799-EB98-437C-A569-9C3B494F4FE2}">
       <formula1>tel_</formula1>
     </dataValidation>
@@ -44089,7 +45547,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:E158"/>
+  <dimension ref="A1:E162"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -46784,9 +48242,77 @@
         <v>104</v>
       </c>
     </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="13">
+        <v>46145</v>
+      </c>
+      <c r="B159" s="7">
+        <v>1</v>
+      </c>
+      <c r="C159" s="8">
+        <v>4</v>
+      </c>
+      <c r="D159" s="8">
+        <v>1</v>
+      </c>
+      <c r="E159" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="13">
+        <v>46145</v>
+      </c>
+      <c r="B160" s="7">
+        <v>2</v>
+      </c>
+      <c r="C160" s="8">
+        <v>7</v>
+      </c>
+      <c r="D160" s="8">
+        <v>1</v>
+      </c>
+      <c r="E160" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="13">
+        <v>46145</v>
+      </c>
+      <c r="B161" s="7">
+        <v>3</v>
+      </c>
+      <c r="C161" s="8">
+        <v>4</v>
+      </c>
+      <c r="D161" s="8">
+        <v>0</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="13">
+        <v>46145</v>
+      </c>
+      <c r="B162" s="7">
+        <v>4</v>
+      </c>
+      <c r="C162" s="8">
+        <v>1</v>
+      </c>
+      <c r="D162" s="8">
+        <v>0</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B158" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B162" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>

--- a/football_stats.xlsx
+++ b/football_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\football_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1412B8A-BA0E-46D5-BA7F-EA2ED4CF0B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D2A6EC5-CB02-4592-B7D4-E4169C4FE75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2735" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2767" uniqueCount="155">
   <si>
     <t>player_id</t>
   </si>
@@ -1427,8 +1427,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J1140" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A1:J1140" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J1155" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:J1155" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G60">
     <sortCondition ref="A1:A60"/>
   </sortState>
@@ -1455,8 +1455,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E162" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E162" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E164" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E164" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{92BE0DCE-EF0C-43B2-937D-640EBFF087A6}" name="date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{B497FB59-180E-4B72-9ECD-E25C88173489}" name="team_number" dataDxfId="3"/>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C2" s="19">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D2" s="19">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1786,15 +1786,15 @@
       </c>
       <c r="E2" s="19">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F2" s="20">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" s="20">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>220</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1814,15 +1814,15 @@
       </c>
       <c r="E3" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F3" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1866,19 +1866,19 @@
       </c>
       <c r="D5" s="21">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" s="21">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F5" s="22">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" s="22">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1894,19 +1894,19 @@
       </c>
       <c r="D6" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F6" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C8" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1954,15 +1954,15 @@
       </c>
       <c r="E8" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F8" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2058,23 +2058,23 @@
       </c>
       <c r="C12" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D12" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E12" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F12" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G12" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2122,15 +2122,15 @@
       </c>
       <c r="E14" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F14" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G14" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2146,19 +2146,19 @@
       </c>
       <c r="D15" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E15" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F15" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>102</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2226,23 +2226,23 @@
       </c>
       <c r="C18" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D18" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E18" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F18" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C21" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D21" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2318,15 +2318,15 @@
       </c>
       <c r="E21" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F21" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G21" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2430,15 +2430,15 @@
       </c>
       <c r="E25" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F25" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G25" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2482,19 +2482,19 @@
       </c>
       <c r="D27" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E27" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F27" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G27" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2822,15 +2822,15 @@
       </c>
       <c r="E39" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F39" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G39" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C84" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D84" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -4082,15 +4082,15 @@
       </c>
       <c r="E84" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F84" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G84" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -5110,23 +5110,23 @@
       </c>
       <c r="C121" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D121" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E121" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F121" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G121" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5618,7 +5618,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:J1140"/>
+  <dimension ref="A1:J1155"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -45524,6 +45524,531 @@
         <v>0</v>
       </c>
       <c r="J1140" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1141" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B1141" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1141" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1141" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Юра Пименов</v>
+      </c>
+      <c r="E1141" s="7">
+        <v>2</v>
+      </c>
+      <c r="F1141" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1141" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H1141" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1141" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1141" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1142" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B1142" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1142" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1142" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Влад</v>
+      </c>
+      <c r="E1142" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1142" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1142" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H1142" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1142" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1142" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1143" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B1143" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1143" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1143" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Паша</v>
+      </c>
+      <c r="E1143" s="7">
+        <v>4</v>
+      </c>
+      <c r="F1143" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1143" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1143" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1143" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1143" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1144" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B1144" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1144" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1144" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Вова</v>
+      </c>
+      <c r="E1144" s="7">
+        <v>3</v>
+      </c>
+      <c r="F1144" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1144" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1144" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1144" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1144" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1145" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B1145" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1145" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1145" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Нурик</v>
+      </c>
+      <c r="E1145" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1145" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1145" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H1145" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1145" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1145" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1146" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B1146" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1146" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1146" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Жора</v>
+      </c>
+      <c r="E1146" s="7">
+        <v>3</v>
+      </c>
+      <c r="F1146" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1146" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1146" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1146" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1146" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1147" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B1147" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1147" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1147" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Макс Логинов</v>
+      </c>
+      <c r="E1147" s="7">
+        <v>3</v>
+      </c>
+      <c r="F1147" s="8">
+        <v>2</v>
+      </c>
+      <c r="G1147" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H1147" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1147" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1147" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1148" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B1148" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1148" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1148" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Александр Костюнин</v>
+      </c>
+      <c r="E1148" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1148" s="8">
+        <v>4</v>
+      </c>
+      <c r="G1148" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1148" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1148" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1148" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1149" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B1149" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1149" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1149" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей Крюков</v>
+      </c>
+      <c r="E1149" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1149" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1149" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1149" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1149" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1149" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1150" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B1150" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1150" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1150" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Олег Шишкин</v>
+      </c>
+      <c r="E1150" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1150" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1150" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1150" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1150" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1150" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1151" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B1151" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1151" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1151" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Костя</v>
+      </c>
+      <c r="E1151" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1151" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1151" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H1151" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1151" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1151" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1152" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B1152" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1152" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1152" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Женя (кипер)</v>
+      </c>
+      <c r="E1152" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1152" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1152" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>6</v>
+      </c>
+      <c r="H1152" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1152" s="10">
+        <v>3</v>
+      </c>
+      <c r="J1152" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1153" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B1153" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1153" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1153" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Кирилл Попов</v>
+      </c>
+      <c r="E1153" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1153" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1153" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H1153" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1153" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1153" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1154" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B1154" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1154" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1154" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Игорь Фомичев</v>
+      </c>
+      <c r="E1154" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1154" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1154" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H1154" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1154" s="10">
+        <v>2</v>
+      </c>
+      <c r="J1154" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1155" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B1155" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1155" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1155" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Миша</v>
+      </c>
+      <c r="E1155" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1155" s="8">
+        <v>2</v>
+      </c>
+      <c r="G1155" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>5</v>
+      </c>
+      <c r="H1155" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1155" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1155" s="16" t="s">
         <v>104</v>
       </c>
     </row>
@@ -45547,7 +46072,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:E162"/>
+  <dimension ref="A1:E164"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -48310,9 +48835,43 @@
         <v>104</v>
       </c>
     </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="13">
+        <v>46149</v>
+      </c>
+      <c r="B163" s="7">
+        <v>1</v>
+      </c>
+      <c r="C163" s="8">
+        <v>5</v>
+      </c>
+      <c r="D163" s="8">
+        <v>1</v>
+      </c>
+      <c r="E163" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="13">
+        <v>46149</v>
+      </c>
+      <c r="B164" s="7">
+        <v>2</v>
+      </c>
+      <c r="C164" s="8">
+        <v>6</v>
+      </c>
+      <c r="D164" s="8">
+        <v>1</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B162" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B164" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>

--- a/football_stats.xlsx
+++ b/football_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\football_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D2A6EC5-CB02-4592-B7D4-E4169C4FE75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441C99D7-89D5-4AD1-9E3F-183BD631F2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2767" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2822" uniqueCount="158">
   <si>
     <t>player_id</t>
   </si>
@@ -520,6 +520,15 @@
   </si>
   <si>
     <t>Артур (АК+1)</t>
+  </si>
+  <si>
+    <t>Валид (АК+1)</t>
+  </si>
+  <si>
+    <t>Никита Марс (АК+1)</t>
+  </si>
+  <si>
+    <t>Крот (АК+1)</t>
   </si>
 </sst>
 </file>
@@ -1398,8 +1407,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G138" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
-  <autoFilter ref="A1:G138" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G141" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
+  <autoFilter ref="A1:G141" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G74">
     <sortCondition descending="1" ref="G1:G74"/>
   </sortState>
@@ -1427,8 +1436,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J1155" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A1:J1155" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J1178" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:J1178" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G60">
     <sortCondition ref="A1:A60"/>
   </sortState>
@@ -1455,8 +1464,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E164" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E164" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E167" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E167" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{92BE0DCE-EF0C-43B2-937D-640EBFF087A6}" name="date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{B497FB59-180E-4B72-9ECD-E25C88173489}" name="team_number" dataDxfId="3"/>
@@ -1734,7 +1743,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" style="38" bestFit="1" customWidth="1"/>
@@ -1778,23 +1787,23 @@
       </c>
       <c r="C2" s="19">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D2" s="19">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" s="19">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F2" s="20">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="20">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1898,15 +1907,15 @@
       </c>
       <c r="E6" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F6" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1946,7 +1955,7 @@
       </c>
       <c r="C8" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1954,15 +1963,15 @@
       </c>
       <c r="E8" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F8" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2122,15 +2131,15 @@
       </c>
       <c r="E14" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F14" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G14" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2146,19 +2155,19 @@
       </c>
       <c r="D15" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E15" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F15" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2422,23 +2431,23 @@
       </c>
       <c r="C25" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E25" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F25" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G25" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2458,15 +2467,15 @@
       </c>
       <c r="E26" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F26" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2590,23 +2599,23 @@
       </c>
       <c r="C31" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E31" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F31" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G31" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2654,15 +2663,15 @@
       </c>
       <c r="E33" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F33" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G33" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2822,15 +2831,15 @@
       </c>
       <c r="E39" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F39" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G39" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2934,15 +2943,15 @@
       </c>
       <c r="E43" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F43" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G43" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3130,15 +3139,15 @@
       </c>
       <c r="E50" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F50" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G50" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3626,7 +3635,7 @@
       </c>
       <c r="C68" s="7">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D68" s="7">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3634,15 +3643,15 @@
       </c>
       <c r="E68" s="7">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F68" s="8">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G68" s="8">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>76</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -4082,15 +4091,15 @@
       </c>
       <c r="E84" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F84" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G84" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4774,7 +4783,7 @@
       </c>
       <c r="C109" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D109" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -4782,15 +4791,15 @@
       </c>
       <c r="E109" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F109" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G109" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -4810,15 +4819,15 @@
       </c>
       <c r="E110" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F110" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G110" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5110,23 +5119,23 @@
       </c>
       <c r="C121" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D121" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E121" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F121" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G121" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5146,15 +5155,15 @@
       </c>
       <c r="E122" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F122" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G122" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5250,7 +5259,7 @@
       </c>
       <c r="C126" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D126" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -5258,15 +5267,15 @@
       </c>
       <c r="E126" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F126" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G126" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -5603,6 +5612,90 @@
       <c r="G138" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
         <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="B139" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="C139" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D139" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E139" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>3</v>
+      </c>
+      <c r="F139" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>2</v>
+      </c>
+      <c r="G139" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="B140" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="C140" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>2</v>
+      </c>
+      <c r="D140" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E140" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>3</v>
+      </c>
+      <c r="F140" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>2</v>
+      </c>
+      <c r="G140" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="B141" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="C141" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D141" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="E141" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>2</v>
+      </c>
+      <c r="F141" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="G141" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5618,7 +5711,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:J1155"/>
+  <dimension ref="A1:J1178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -46049,6 +46142,811 @@
         <v>0</v>
       </c>
       <c r="J1155" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1156" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1156" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1156" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1156" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Кирилл Попов</v>
+      </c>
+      <c r="E1156" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1156" s="8">
+        <v>2</v>
+      </c>
+      <c r="G1156" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1156" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1156" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1156" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1157" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1157" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1157" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1157" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Олег Шишкин</v>
+      </c>
+      <c r="E1157" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1157" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1157" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1157" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1157" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1157" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1158" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1158" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1158" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1158" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Александр Костюнин</v>
+      </c>
+      <c r="E1158" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1158" s="8">
+        <v>3</v>
+      </c>
+      <c r="G1158" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1158" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1158" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1158" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1159" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1159" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1159" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1159" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Иван</v>
+      </c>
+      <c r="E1159" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1159" s="8">
+        <v>2</v>
+      </c>
+      <c r="G1159" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1159" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1159" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1159" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1160" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1160" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1160" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1160" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Богдан Ждамаров</v>
+      </c>
+      <c r="E1160" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1160" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1160" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1160" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1160" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1160" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1161" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1161" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1161" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1161" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Егор (АК+1)</v>
+      </c>
+      <c r="E1161" s="7">
+        <v>7</v>
+      </c>
+      <c r="F1161" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1161" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1161" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1161" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1161" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1162" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1162" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1162" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1162" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Андрей (АК+1)</v>
+      </c>
+      <c r="E1162" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1162" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1162" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1162" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1162" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1162" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1163" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1163" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1163" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1163" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Макс Логинов</v>
+      </c>
+      <c r="E1163" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1163" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1163" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H1163" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1163" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1163" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1164" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1164" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1164" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1164" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Женя (кипер)</v>
+      </c>
+      <c r="E1164" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1164" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1164" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H1164" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1164" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1164" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1165" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1165" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1165" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1165" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Рамиль (АК+1)</v>
+      </c>
+      <c r="E1165" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1165" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1165" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H1165" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1165" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1165" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1166" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1166" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1166" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1166" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Коля (АК+1)</v>
+      </c>
+      <c r="E1166" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1166" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1166" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H1166" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1166" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1166" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1167" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1167" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1167" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1167" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Кирилл (АК+1)</v>
+      </c>
+      <c r="E1167" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1167" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1167" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H1167" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1167" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1167" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1168" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1168" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1168" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1168" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Макс (АК+1)</v>
+      </c>
+      <c r="E1168" s="7">
+        <v>3</v>
+      </c>
+      <c r="F1168" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1168" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H1168" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1168" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1168" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1169" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1169" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1169" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1169" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Валид (АК+1)</v>
+      </c>
+      <c r="E1169" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1169" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1169" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H1169" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1169" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1169" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1170" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1170" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1170" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1170" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Никита Марс (АК+1)</v>
+      </c>
+      <c r="E1170" s="7">
+        <v>2</v>
+      </c>
+      <c r="F1170" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1170" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H1170" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="I1170" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1170" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1171" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1171" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1171" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1171" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей Крюков</v>
+      </c>
+      <c r="E1171" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1171" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1171" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1171" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1171" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1171" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1172" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1172" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1172" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1172" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Паша</v>
+      </c>
+      <c r="E1172" s="7">
+        <v>4</v>
+      </c>
+      <c r="F1172" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1172" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1172" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1172" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1172" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1173" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1173" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1173" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1173" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Жора</v>
+      </c>
+      <c r="E1173" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1173" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1173" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1173" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1173" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1173" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1174" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1174" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1174" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1174" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Нурик</v>
+      </c>
+      <c r="E1174" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1174" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1174" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1174" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1174" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1174" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1175" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1175" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1175" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1175" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Эля</v>
+      </c>
+      <c r="E1175" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1175" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1175" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1175" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1175" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1175" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1176" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1176" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1176" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1176" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Семен (АК+1)</v>
+      </c>
+      <c r="E1176" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1176" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1176" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1176" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1176" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1176" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1177" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1177" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1177" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1177" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Егор (АК+1)</v>
+      </c>
+      <c r="E1177" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1177" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1177" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1177" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1177" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1177" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1178" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B1178" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1178" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1178" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Крот (АК+1)</v>
+      </c>
+      <c r="E1178" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1178" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1178" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>2</v>
+      </c>
+      <c r="H1178" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1178" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1178" s="16" t="s">
         <v>104</v>
       </c>
     </row>
@@ -46072,7 +46970,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:E164"/>
+  <dimension ref="A1:E167"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -48869,9 +49767,60 @@
         <v>104</v>
       </c>
     </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="13">
+        <v>46156</v>
+      </c>
+      <c r="B165" s="7">
+        <v>1</v>
+      </c>
+      <c r="C165" s="8">
+        <v>4</v>
+      </c>
+      <c r="D165" s="8">
+        <v>1</v>
+      </c>
+      <c r="E165" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="13">
+        <v>46156</v>
+      </c>
+      <c r="B166" s="7">
+        <v>2</v>
+      </c>
+      <c r="C166" s="8">
+        <v>3</v>
+      </c>
+      <c r="D166" s="8">
+        <v>2</v>
+      </c>
+      <c r="E166" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="13">
+        <v>46156</v>
+      </c>
+      <c r="B167" s="7">
+        <v>3</v>
+      </c>
+      <c r="C167" s="8">
+        <v>2</v>
+      </c>
+      <c r="D167" s="8">
+        <v>1</v>
+      </c>
+      <c r="E167" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B164" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B167" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>

--- a/football_stats.xlsx
+++ b/football_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\football_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441C99D7-89D5-4AD1-9E3F-183BD631F2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE2E2F4B-4F6B-4168-90F0-DBF857105C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2822" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2898" uniqueCount="161">
   <si>
     <t>player_id</t>
   </si>
@@ -529,6 +529,15 @@
   </si>
   <si>
     <t>Крот (АК+1)</t>
+  </si>
+  <si>
+    <t>Иван (ФИО)</t>
+  </si>
+  <si>
+    <t>Ислам</t>
+  </si>
+  <si>
+    <t>Мара (Атай+1)</t>
   </si>
 </sst>
 </file>
@@ -1407,8 +1416,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G141" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
-  <autoFilter ref="A1:G141" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}" name="_players" displayName="_players" ref="A1:G144" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
+  <autoFilter ref="A1:G144" xr:uid="{CC58E8C5-7B8B-42F7-9BFF-85AAC284233D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G74">
     <sortCondition descending="1" ref="G1:G74"/>
   </sortState>
@@ -1436,8 +1445,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J1178" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
-  <autoFilter ref="A1:J1178" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}" name="_stats" displayName="_stats" ref="A1:J1211" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+  <autoFilter ref="A1:J1211" xr:uid="{D3D1149F-12DA-4A23-97C8-9D9CCA1140FB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G60">
     <sortCondition ref="A1:A60"/>
   </sortState>
@@ -1464,8 +1473,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E167" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E167" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}" name="_teams" displayName="_teams" ref="A1:E171" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E171" xr:uid="{B6423DC2-EC3F-4914-9E08-BC4E7C6626C9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{92BE0DCE-EF0C-43B2-937D-640EBFF087A6}" name="date" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{B497FB59-180E-4B72-9ECD-E25C88173489}" name="team_number" dataDxfId="3"/>
@@ -1743,7 +1752,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" style="38" bestFit="1" customWidth="1"/>
@@ -1815,23 +1824,23 @@
       </c>
       <c r="C3" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D3" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="F3" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>286</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1847,11 +1856,11 @@
       </c>
       <c r="D4" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F4" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1859,7 +1868,7 @@
       </c>
       <c r="G4" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1879,7 +1888,7 @@
       </c>
       <c r="E5" s="21">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F5" s="22">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1887,7 +1896,7 @@
       </c>
       <c r="G5" s="22">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1899,7 +1908,7 @@
       </c>
       <c r="C6" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1907,7 +1916,7 @@
       </c>
       <c r="E6" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F6" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1915,7 +1924,7 @@
       </c>
       <c r="G6" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1927,23 +1936,23 @@
       </c>
       <c r="C7" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D7" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E7" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F7" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>211</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1955,15 +1964,15 @@
       </c>
       <c r="C8" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F8" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1971,7 +1980,7 @@
       </c>
       <c r="G8" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2067,7 +2076,7 @@
       </c>
       <c r="C12" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D12" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2075,7 +2084,7 @@
       </c>
       <c r="E12" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F12" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2083,7 +2092,7 @@
       </c>
       <c r="G12" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2127,11 +2136,11 @@
       </c>
       <c r="D14" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F14" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2139,7 +2148,7 @@
       </c>
       <c r="G14" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2179,23 +2188,23 @@
       </c>
       <c r="C16" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D16" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E16" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F16" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>97</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2215,15 +2224,15 @@
       </c>
       <c r="E17" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F17" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2235,23 +2244,23 @@
       </c>
       <c r="C18" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D18" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F18" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2299,15 +2308,15 @@
       </c>
       <c r="E20" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F20" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G20" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2319,15 +2328,15 @@
       </c>
       <c r="C21" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D21" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E21" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F21" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2335,7 +2344,7 @@
       </c>
       <c r="G21" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2351,19 +2360,19 @@
       </c>
       <c r="D22" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F22" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G22" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2375,23 +2384,23 @@
       </c>
       <c r="C23" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D23" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E23" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F23" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G23" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>196</v>
+        <v>213</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2467,15 +2476,15 @@
       </c>
       <c r="E26" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F26" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G26" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2655,7 +2664,7 @@
       </c>
       <c r="C33" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D33" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2663,15 +2672,15 @@
       </c>
       <c r="E33" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F33" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G33" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2711,7 +2720,7 @@
       </c>
       <c r="C35" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D35" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2719,7 +2728,7 @@
       </c>
       <c r="E35" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F35" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2727,7 +2736,7 @@
       </c>
       <c r="G35" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2795,7 +2804,7 @@
       </c>
       <c r="C38" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D38" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2803,15 +2812,15 @@
       </c>
       <c r="E38" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F38" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G38" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2831,7 +2840,7 @@
       </c>
       <c r="E39" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F39" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2839,7 +2848,7 @@
       </c>
       <c r="G39" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2887,7 +2896,7 @@
       </c>
       <c r="E41" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F41" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2895,7 +2904,7 @@
       </c>
       <c r="G41" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2907,23 +2916,23 @@
       </c>
       <c r="C42" s="16">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D42" s="16">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E42" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F42" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G42" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2939,11 +2948,11 @@
       </c>
       <c r="D43" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E43" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F43" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2951,7 +2960,7 @@
       </c>
       <c r="G43" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3139,7 +3148,7 @@
       </c>
       <c r="E50" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F50" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3147,7 +3156,7 @@
       </c>
       <c r="G50" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3531,15 +3540,15 @@
       </c>
       <c r="E64" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F64" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G64" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -4819,7 +4828,7 @@
       </c>
       <c r="E110" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F110" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -4827,7 +4836,7 @@
       </c>
       <c r="G110" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -5099,15 +5108,15 @@
       </c>
       <c r="E120" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F120" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G120" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5123,11 +5132,11 @@
       </c>
       <c r="D121" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E121" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F121" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -5135,7 +5144,7 @@
       </c>
       <c r="G121" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -5491,7 +5500,7 @@
       </c>
       <c r="E134" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F134" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -5499,7 +5508,7 @@
       </c>
       <c r="G134" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -5575,15 +5584,15 @@
       </c>
       <c r="E137" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F137" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G137" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -5694,6 +5703,90 @@
         <v>1</v>
       </c>
       <c r="G141" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="B142" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="C142" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D142" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E142" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="F142" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="G142" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="B143" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="C143" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D143" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E143" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>4</v>
+      </c>
+      <c r="F143" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="G143" s="18">
+        <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="B144" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="C144" s="10">
+        <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="D144" s="10">
+        <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>0</v>
+      </c>
+      <c r="E144" s="10">
+        <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>3</v>
+      </c>
+      <c r="F144" s="18">
+        <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
+        <v>1</v>
+      </c>
+      <c r="G144" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
         <v>4</v>
       </c>
@@ -5711,7 +5804,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:J1178"/>
+  <dimension ref="A1:J1211"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -46947,6 +47040,1161 @@
         <v>0</v>
       </c>
       <c r="J1178" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1179" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1179" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1179" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1179" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Витя</v>
+      </c>
+      <c r="E1179" s="7">
+        <v>5</v>
+      </c>
+      <c r="F1179" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1179" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>10</v>
+      </c>
+      <c r="H1179" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1179" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1179" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1180" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1180" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1180" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1180" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Вова</v>
+      </c>
+      <c r="E1180" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1180" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1180" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H1180" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1180" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1180" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1181" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1181" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1181" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1181" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Дима Сахаров</v>
+      </c>
+      <c r="E1181" s="7">
+        <v>2</v>
+      </c>
+      <c r="F1181" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1181" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>10</v>
+      </c>
+      <c r="H1181" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1181" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1181" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1182" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1182" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1182" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1182" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Максим Строцкий</v>
+      </c>
+      <c r="E1182" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1182" s="8">
+        <v>5</v>
+      </c>
+      <c r="G1182" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>10</v>
+      </c>
+      <c r="H1182" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1182" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1182" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1183" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1183" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1183" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1183" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Арги</v>
+      </c>
+      <c r="E1183" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1183" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1183" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H1183" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1183" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1183" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1184" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1184" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1184" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1184" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Анашкин</v>
+      </c>
+      <c r="E1184" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1184" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1184" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>10</v>
+      </c>
+      <c r="H1184" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1184" s="10">
+        <v>2</v>
+      </c>
+      <c r="J1184" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1185" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1185" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1185" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1185" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Костя</v>
+      </c>
+      <c r="E1185" s="7">
+        <v>3</v>
+      </c>
+      <c r="F1185" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1185" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>10</v>
+      </c>
+      <c r="H1185" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1185" s="10">
+        <v>2</v>
+      </c>
+      <c r="J1185" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1186" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1186" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1186" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1186" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей Крюков</v>
+      </c>
+      <c r="E1186" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1186" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1186" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1186" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1186" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1186" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1187" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1187" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1187" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1187" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Олег Шишкин</v>
+      </c>
+      <c r="E1187" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1187" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1187" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1187" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1187" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1187" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1188" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1188" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1188" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1188" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Никита</v>
+      </c>
+      <c r="E1188" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1188" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1188" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H1188" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1188" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1188" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1189" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1189" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1189" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1189" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Макс Логинов</v>
+      </c>
+      <c r="E1189" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1189" s="8">
+        <v>3</v>
+      </c>
+      <c r="G1189" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1189" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1189" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1189" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1190" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1190" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1190" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1190" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Женя (кипер)</v>
+      </c>
+      <c r="E1190" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1190" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1190" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1190" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1190" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1190" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1191" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1191" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1191" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1191" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Богдан Ждамаров</v>
+      </c>
+      <c r="E1191" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1191" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1191" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1191" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1191" s="10">
+        <v>2</v>
+      </c>
+      <c r="J1191" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1192" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1192" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1192" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1192" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сергей</v>
+      </c>
+      <c r="E1192" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1192" s="8">
+        <v>2</v>
+      </c>
+      <c r="G1192" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1192" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1192" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1192" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1193" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1193" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1193" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1193" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Толя Шлаев</v>
+      </c>
+      <c r="E1193" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1193" s="8">
+        <v>2</v>
+      </c>
+      <c r="G1193" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>10</v>
+      </c>
+      <c r="H1193" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1193" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1193" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1194" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1194" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1194" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1194" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Эля</v>
+      </c>
+      <c r="E1194" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1194" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1194" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>10</v>
+      </c>
+      <c r="H1194" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1194" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1194" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1195" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1195" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1195" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1195" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Андрей (АК+1)</v>
+      </c>
+      <c r="E1195" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1195" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1195" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1195" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1195" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1195" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1196" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1196" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1196" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1196" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Кирилл (АК+1)</v>
+      </c>
+      <c r="E1196" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1196" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1196" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1196" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1196" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1196" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1197" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1197" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1197" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1197" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Рома Сурнин</v>
+      </c>
+      <c r="E1197" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1197" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1197" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1197" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1197" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1197" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1198" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1198" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1198" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1198" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Сурэн</v>
+      </c>
+      <c r="E1198" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1198" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1198" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H1198" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1198" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1198" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1199" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1199" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1199" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D1199" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Иван (ФИО)</v>
+      </c>
+      <c r="E1199" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1199" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1199" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1199" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1199" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1199" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1200" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1200" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1200" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1200" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Игорь Фомичев</v>
+      </c>
+      <c r="E1200" s="7">
+        <v>3</v>
+      </c>
+      <c r="F1200" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1200" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1200" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1200" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1200" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1201" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1201" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1201" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1201" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Ислам</v>
+      </c>
+      <c r="E1201" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1201" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1201" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1201" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1201" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1201" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1202" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1202" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1202" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1202" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Рамиль (АК+1)</v>
+      </c>
+      <c r="E1202" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1202" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1202" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H1202" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1202" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1202" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1203" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1203" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1203" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1203" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Эльдар</v>
+      </c>
+      <c r="E1203" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1203" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1203" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1203" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1203" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1203" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1204" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1204" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1204" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1204" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Юра Пименов</v>
+      </c>
+      <c r="E1204" s="7">
+        <v>4</v>
+      </c>
+      <c r="F1204" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1204" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1204" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1204" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1204" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1205" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1205" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1205" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1205" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Расул</v>
+      </c>
+      <c r="E1205" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1205" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1205" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H1205" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1205" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1205" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1206" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1206" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1206" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1206" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Атай</v>
+      </c>
+      <c r="E1206" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1206" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1206" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H1206" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1206" s="10">
+        <v>1</v>
+      </c>
+      <c r="J1206" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1207" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1207" s="7">
+        <v>1</v>
+      </c>
+      <c r="C1207" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1207" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Мара (Атай+1)</v>
+      </c>
+      <c r="E1207" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1207" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1207" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>3</v>
+      </c>
+      <c r="H1207" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1207" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1207" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1208" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1208" s="7">
+        <v>2</v>
+      </c>
+      <c r="C1208" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1208" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Мухамед (Руб+1)</v>
+      </c>
+      <c r="E1208" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1208" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1208" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>4</v>
+      </c>
+      <c r="H1208" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1208" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1208" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1209" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1209" s="7">
+        <v>4</v>
+      </c>
+      <c r="C1209" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1209" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Александр Травкин</v>
+      </c>
+      <c r="E1209" s="7">
+        <v>5</v>
+      </c>
+      <c r="F1209" s="8">
+        <v>4</v>
+      </c>
+      <c r="G1209" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>10</v>
+      </c>
+      <c r="H1209" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="I1209" s="10">
+        <v>3</v>
+      </c>
+      <c r="J1209" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1210" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1210" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1210" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1210" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Нурик</v>
+      </c>
+      <c r="E1210" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1210" s="8">
+        <v>1</v>
+      </c>
+      <c r="G1210" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1210" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1210" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1210" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1211" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B1211" s="7">
+        <v>3</v>
+      </c>
+      <c r="C1211" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1211" s="10" t="str">
+        <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
+        <v>Влад</v>
+      </c>
+      <c r="E1211" s="7">
+        <v>0</v>
+      </c>
+      <c r="F1211" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1211" s="10">
+        <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>1</v>
+      </c>
+      <c r="H1211" s="10">
+        <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
+        <v>0</v>
+      </c>
+      <c r="I1211" s="10">
+        <v>0</v>
+      </c>
+      <c r="J1211" s="16" t="s">
         <v>104</v>
       </c>
     </row>
@@ -46970,7 +48218,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:E167"/>
+  <dimension ref="A1:E171"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -49818,9 +51066,77 @@
         <v>104</v>
       </c>
     </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="13">
+        <v>46159</v>
+      </c>
+      <c r="B168" s="7">
+        <v>1</v>
+      </c>
+      <c r="C168" s="8">
+        <v>3</v>
+      </c>
+      <c r="D168" s="8">
+        <v>1</v>
+      </c>
+      <c r="E168" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="13">
+        <v>46159</v>
+      </c>
+      <c r="B169" s="7">
+        <v>2</v>
+      </c>
+      <c r="C169" s="8">
+        <v>4</v>
+      </c>
+      <c r="D169" s="8">
+        <v>0</v>
+      </c>
+      <c r="E169" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="13">
+        <v>46159</v>
+      </c>
+      <c r="B170" s="7">
+        <v>3</v>
+      </c>
+      <c r="C170" s="8">
+        <v>1</v>
+      </c>
+      <c r="D170" s="8">
+        <v>0</v>
+      </c>
+      <c r="E170" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="13">
+        <v>46159</v>
+      </c>
+      <c r="B171" s="7">
+        <v>4</v>
+      </c>
+      <c r="C171" s="8">
+        <v>10</v>
+      </c>
+      <c r="D171" s="8">
+        <v>1</v>
+      </c>
+      <c r="E171" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B167" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B171" xr:uid="{FB33A308-4E41-4174-AACA-4EC901547F19}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>

--- a/football_stats.xlsx
+++ b/football_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\football_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE2E2F4B-4F6B-4168-90F0-DBF857105C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D6A4282-7EB0-4012-9B9E-271B1EDEB2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="C3" s="11">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="E3" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F3" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="G3" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E7" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F7" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="G7" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E16" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F16" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="G16" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E22" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F22" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="G22" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2388,11 +2388,11 @@
       </c>
       <c r="D23" s="11">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E23" s="11">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F23" s="12">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="G23" s="12">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="E26" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F26" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="G26" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="E42" s="16">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F42" s="17">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="G42" s="17">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="C64" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D64" s="10">
         <f>SUMIFS(_stats[assists_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="E64" s="10">
         <f>SUMIFS(_stats[wins_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F64" s="18">
         <f>SUMIFS(_stats[draws_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="G64" s="18">
         <f>SUM(_players[[#This Row],[goals]:[draws]])</f>
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -47061,11 +47061,11 @@
         <v>5</v>
       </c>
       <c r="F1179" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1179" s="10">
         <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1179" s="10">
         <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
@@ -47135,7 +47135,7 @@
       </c>
       <c r="G1181" s="10">
         <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1181" s="10">
         <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
@@ -47170,7 +47170,7 @@
       </c>
       <c r="G1182" s="10">
         <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1182" s="10">
         <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
@@ -47233,14 +47233,14 @@
         <v>Анашкин</v>
       </c>
       <c r="E1184" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1184" s="8">
         <v>0</v>
       </c>
       <c r="G1184" s="10">
         <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1184" s="10">
         <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
@@ -47268,14 +47268,14 @@
         <v>Костя</v>
       </c>
       <c r="E1185" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1185" s="8">
         <v>1</v>
       </c>
       <c r="G1185" s="10">
         <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1185" s="10">
         <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
@@ -47555,7 +47555,7 @@
       </c>
       <c r="G1193" s="10">
         <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1193" s="10">
         <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
@@ -47590,7 +47590,7 @@
       </c>
       <c r="G1194" s="10">
         <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1194" s="10">
         <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
@@ -48115,14 +48115,14 @@
       </c>
       <c r="G1209" s="10">
         <f>SUMIFS(_teams[wins_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H1209" s="10">
         <f>SUMIFS(_teams[draws_on_date],_teams[date],_stats[[#This Row],[date]],_teams[team_number],_stats[[#This Row],[team_number]])</f>
         <v>1</v>
       </c>
       <c r="I1209" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J1209" s="16" t="s">
         <v>104</v>
@@ -51125,7 +51125,7 @@
         <v>4</v>
       </c>
       <c r="C171" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D171" s="8">
         <v>1</v>

--- a/football_stats.xlsx
+++ b/football_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\football_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D6A4282-7EB0-4012-9B9E-271B1EDEB2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B49354-711B-4C72-ABA9-729367FEB26F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -531,13 +531,13 @@
     <t>Крот (АК+1)</t>
   </si>
   <si>
-    <t>Иван (ФИО)</t>
-  </si>
-  <si>
     <t>Ислам</t>
   </si>
   <si>
     <t>Мара (Атай+1)</t>
+  </si>
+  <si>
+    <t>Иван Канунцев</t>
   </si>
 </sst>
 </file>
@@ -5709,10 +5709,10 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="36" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B142" s="36" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C142" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B143" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C143" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -5765,10 +5765,10 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B144" s="36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C144" s="10">
         <f>SUMIFS(_stats[goals_on_date],_stats[player_id],_players[[#This Row],[player_id]])</f>
@@ -47751,11 +47751,11 @@
         <v>3</v>
       </c>
       <c r="C1199" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D1199" s="10" t="str">
         <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
-        <v>Иван (ФИО)</v>
+        <v>Иван Канунцев</v>
       </c>
       <c r="E1199" s="7">
         <v>0</v>
@@ -47821,7 +47821,7 @@
         <v>2</v>
       </c>
       <c r="C1201" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D1201" s="10" t="str">
         <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
@@ -48031,7 +48031,7 @@
         <v>1</v>
       </c>
       <c r="C1207" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D1207" s="10" t="str">
         <f>IFERROR(VLOOKUP(_stats[[#This Row],[player_id]],_players[[player_id]:[player_name]],2,0),"")</f>
